--- a/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
+++ b/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
@@ -8,11 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заводы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы и обратные" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы и обратные" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Покрытие'!$A$1:$E$153</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +55,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,13 +99,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -458,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -557,13 +584,1031 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>поиск заводов идёт — лист заполнится после проверки</t>
-        </is>
-      </c>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Челябинск (ул. Енисейская, 56)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Стальные: КШЦП (под приварку) Ду15–200, КШЦФ полнопроходные/неполнопроходные Ду15–250, 11с67п КШРФ (разборный фланцевый, в т.ч. «компактный» укороченный L=66–160 мм) Ду25–200 — совпадает с обозначение</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Да, на карточках товаров: «Реестровый номер ПП» 10655491 (стальные КШЦФ/КШЦП/КШЦМ), 10714005 (11с67п КШРФ), 10657717 (КШ</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>+7 (351) 730-47-47</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>office@chsgs.ru</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>лд.рф (xn--d1an.xn--p1ai), chsgs.ru → редирект</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: +7 351 730-47-47 и office@chsgs.ru — в подвале главной страницы и на странице «Контакты» (адрес: Челябинск, Енисейская, 56; ИНН 7447276227). Доп.: от</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://xn--d1an.xn--p1ai/catalog/krany/krany-stalnye/</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Челябинск (ул. Складская, 1)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Для жидких сред: приварные полнопроходные DN15–500 (PN40 до DN65, PN25 далее) и редуцированные; фланцевые полнопроходные DN15–500 (PN40 до DN50, PN16/25 DN65+) и редуцированные (в т.ч. DN250/200 PN16 </t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Да: выписка из реестра российской промышленной продукции № 10647852 от 16.06.2025 (внесено 11.06.2025, срок до 10.06.202</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>8-800-444-74-74</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>info@alsoarm.ru</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>alsoarm.ru</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: 8-800-444-74-74 и info@alsoarm.ru — в шапке/подвале главной и на странице «Контакты» (адрес завода г. Челябинск, ул. Складская, 1). Филиалы: Москва t</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://alsoarm.ru/catalog/dlya-zhidkikh-sred/privarnye/polnoprokhodnye/</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Краны Балашихи» (КБ)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Балашиха, Московская обл. (ул. 1 Мая, 10Б, мкр. Саввино)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Приварные стандартнопроходные Ду15–200 (Ру40 до Ду50, Ру25 далее) → все «11с67п цельносварной под приварку»; фланцевые стандартнопроходные Ду15–200 и полнопроходные Ду15–125 (Ру40/16/25) → 11с22п, 11С</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>не найдено (на сайте kb-arm.ru упоминания записи в реестре Минпромторга не найдено; запросить выписку, ИНН по данным кат</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>+7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>sales@kb-arm.ru</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>kb-arm.ru</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: +7 (495) 27-55-888 и sales@kb-arm.ru — в шапке и подвале главной страницы и на странице «Контакты» (адрес производства тот же).</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://kb-arm.ru/product/voda/krany-privarnye/</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>ЛЗТА «Маршал» (Луганский завод трубопроводной арматуры); сайт и продажи — ООО «Арматура М», официальный дистрибьютор завода</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Луганск (ул. Монтажная, 13); склад/офис — Московская обл., г. Дзержинский, ул. Алексеевская, 5</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ТОЧНЫЕ обозначения из ТЗ: «11с67п ЦУФ.00.1» (цельносварной укороченный фланцевый полнопроходной Ду15–200 Ру16/25/40) = «ЦУФ.001 КШ» в ТЗ; «10нж45фт-01 ЦУФ» и «10нж45/46/47фт-01 2ЦФ» (корпус 12Х18Н10Т,</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Да (по тексту главной страницы): «Заключение о подтверждении производства промышленной продукции на территории РФ № 2665</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>8 (800) 301-20-50; +7 (495) 223-74-04</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>info@lztamarshal.ru</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>lztamarshal.ru</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Совпадает: 8 800 301 20 50, +7 (495) 223-74-04 и info@lztamarshal.ru — в шапке и подвале главной и на странице «Контакты». Завод в Луганске на той же странице: </t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://lztamarshal.ru/catalog/detail/kran_sharovoy_ukorochennyy_flantsevyy_st_20_pod_zadvizhku/</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ТЕМПЕР» (завод TEMPER)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Курган (ул. Щорса, 93А); филиал/склад в Хабаровске (ул. М. Горького, 57а)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1.6/82 «TEMPER 28020025» — оригинал российского завода (Курган): кран 280 муфтовый станд.-проходной, арт. 28020025 = DN25 PN40, -40…+200 °С — замена не требуется. Стальные: 292 приварной полнопроходно</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Да (частично): на https://temper.ru/license/index — «Заключение Минпромторга о внесении в реестр латунных шаровых кранов</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>+7 (3522) 22-88-88</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>temper@temper.ru</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>temper.ru</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: +7(3522)22-88-88 и temper@temper.ru — в шапке/подвале главной и на странице «Контакты» (адрес производства Курган, Щорса 93А). Хабаровск: +7 (421) 24</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://temper.ru/catalog/product/kran-sarovoj-standartnoprohodnoj-280-muftovyj</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>РОБЕН (ранее БРОЕН; ТМ «Балломакс») — завод в Коломне</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Московская обл., г. Коломна, с. Нижнее Хорошово, ул. Николая Птицына, 42</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каталог «Балломакс» КШТ 60/61 (DE_catalog_2026_09.pdf): сварка/сварка станд. DN10–1400 и полнопроходные DN15–1400; фланец/фланец станд. DN15–900 и полнопроходные DN15–1000 (PN16/25/40); резьба/резьба </t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да (по тексту https://robenvalves.ru/abouthtml): «Продукция РОБЕН производится в России и внесена в Реестр промышленной </t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>+7 (495) 228-11-50</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>info@robenvalves.ru</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>robenvalves.ru (broen.ru → редирект)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: +7 (495) 228-11-50 и info@robenvalves.ru — в шапке/подвале главной (4 упоминания) и на странице «Контакты».</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://broen.ru/docfiles/de-valves/DE_catalog_2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура» (ТМ КИПИКА)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Пенза (ул. Аустрина, 143А)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Кран трёхходовой для манометра 11б18бк(у)/11б18бк(ф) Ду15 Ру16, корпус ЛЦ40Сд, пар до +225 °С, вода до +140 °С, G1/2×M20×1,5 → 1.3/39, 1.6/16 точно; 1.3/100 и 1.6/50 («шаровой 11б27п(м) 3-ход.») — ана</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8412) 909-200; +7 (8412) 909-300</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>b18bk@11b18bk.ru</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>11b18bk.ru</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Совпадает: +7(8412)909-200/909-300 и b18bk@11b18bk.ru — в шапке, подвале («Контактная информация») и на странице «Контакты» (ИНН 5835036366).</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://11b18bk.ru/13-krany-probkovye</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» (бренды «Гранвэл», «Гранлок»)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Московская обл. (производственный комплекс, 4 цеха, &gt;31 000 м²; адрес площадки на сайте не указан; склад — Лыткарино; «Ступино» на сайте НЕ подтверждено)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91, 1.3/32, 1.3/33, 1.3/34</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Оригинал позиций ТЗ: ЗПВС-FL(W)-3-…-MN-E/MR-E (= «FL(w)-3-MR-E», «ЗПВС») DN65/80/100/150/200 PN16 и ЗПТЛ-FLN(W)-5-…-HT (= «ЗП ТЛ», седло EPDM HT, до +130 °C) DN80/100/150/200 PN16 — все 12 чугунных ме</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>На сайте: «дисковые поворотные затворы «Гранвэл»» — в числе продукции с заключением Минпромторга по ПП 719 (новость 11.0</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>+7 (495) 937-89-68; Владивосток +7 (984) 159-21-64</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>info@adl.ru; granvel@adl.ru</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://adl.ru</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>+7 (495) 937-89-68 и info@adl.ru — в шапке каждой страницы и на странице «Контакты» (центральный офис: Москва, пр-т Андропова, 18, корп. 7); granvel@adl.ru — на</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://adl.ru/truboprovodnaya-armatura/zatvory-diskovye-povorotnye/filter/brend-granvel/</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» (ОАО «ЛМЗ»)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Нижегородская обл., г. Семёнов, ул. Промышленная, 3</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1.3/154, 1.3/155, 1.3/156, 1.3/158, 1.3/159, 1.3/161, 1.6/89, 1.6/90, 1.6/91</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Затвор 32ч1р межфланцевый с рукояткой, корпус/диск СЧ20 (DN50–150), манжета EPDM, класс А, PN16 для DN50–150, до +115 °C. DN200 — только PN10 (ВЧ50) → 1.3/157 и 1.3/160 (Ду200 Ру16) НЕ закрывает; DN65</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>На сайте: «продукция нашего завода внесена в реестр Минпромторга» (новость 16.05.2025, https://www.semlmz.ru/novosti), п</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>+7 (83162) 5-70-90</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>marketlmz@mail.ru</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.semlmz.ru</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7 (83162) 5-70-90 — в шапке, подвале и на странице «Контакты»; marketlmz@mail.ru — в шапке всех страниц и mailto на главной (на «Контактах» адреса руководства </t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.semlmz.ru/zatvor-32ch1r</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91, 1.1/22, 1.1/23</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>+7 (351) 307-71-09</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>info@aoutk.ru</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://aoutk.ru</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>+73513077109 и info@aoutk.ru — в шапке всех страниц и на странице «Контакты» (факт. адрес Озёрск, Индустриальная, 4). Совпадает.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://aoutk.ru/catalog/butterfly-valves/elastomeric-seat/</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПромАрм» (PromArm®)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>1.1/23, 1.1/22, 1.3/150, 1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гигиенический; упоминаний реестра ПП 719 не</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>info@promarm.ru</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8412) 35-07-97 и +7 (495) 668-10-92 — в подвале каждой страницы и на «Контактах» (7 вхождений); info@promarm.ru — в шапке и на «Контактах» (12 вхождений). В</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.promarm.com/catalog/pipeline_valves/butterfly_valves/pa_900/zatvor_pa_954_450_10_05_dn_450_pn_10/</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>г. Пенза (промкомплекс 225 000 м²)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1.3/150, 1.1/23, 1.1/22</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>не найдено на сайте</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>8 800 444-00-28 (продажи)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>sales@ptpa.ru</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://ptpa.ru</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>8 800 444-00-28 и sales@ptpa.ru — в шапке всех страниц и на «Контактах» (отдел продаж). Совпадает.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://ptpa.ru/catalog/zatvory-diskovye/zatvory-diskovye-povorotnye-stalnye/</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоПромАтомСервис» (ООО «ЭПАС»)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>г. Екатеринбург, ул. Электриков, 18Б</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1.3/151, 1.3/152, 1.3/153</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Точная маркировка ТЗ: «ЗДП-150-6,3-1-М-А-УХЛ1» (конфигуратор на карточке), ЗДП-50/80/100/125/150/200, PN 0,63 МПа, корпус и диск — алюминий АК12оч, класс А, рукоятка, для трансформаторного масла. «Зат</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 211-02-63 (комплектующие для трансформаторов)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>epas-z@mail.ru</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://epasworld.com</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 211-02-63 и epas-z@mail.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://epasworld.com/product/%D0%B7%D0%B4%D0%BF150/</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго» / ООО «Лидер-Энерго» (одна группа, сайт lider-energo.ru)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>г. Тольятти, ул. 40 лет Победы, 14 (литейный, механический, сборочный цеха — «производится нашей производственной компанией ООО Транс-Энерго»)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1.3/151, 1.3/152, 1.3/153</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Держатель ТУ из ТЗ: каталог ЗПД — «затворы поворотные дисковые … изготавливаемые по ТУ 28.14.13-012-09338969-2019», ЗПД-50/80/100/125/150/200, Pном 0,63 МПа, трансформаторное масло, УХЛ1, класс А, руч</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>не найдено (поиск по сайту «реестр» — 0 результатов)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8482) 21-66-32</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>trans-energo@bk.ru</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://lider-energo.ru</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8482) 21-66-32 и trans-energo@bk.ru — в шапке всех страниц и на «Контактах» (там же info@lider-energo.ru). Совпадает.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://lider-energo.ru/product/zatvory-diskovye-povorotnye-du-150-transformatornye</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1.3/163, 1.6/93</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>не найдено на сайте</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8352) 30-51-48</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>sales@zeim.ru</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zeim.ru</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>+7 (8352) 30-51-48 (= «(8352) 305-148» в подвале) и sales@zeim.ru — на «Контактах» и в подвале всех страниц. Совпадает.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zeim.ru/production/mep/</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>8 (843) 558-25-28</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>info@promav.ru</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.promav.ru</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>8(843)558-25-28 и info@promav.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.promav.ru/catalog/ustrojstva-avtomatizatsii/mep/</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПКФ «ТЕРМ»</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>г. Саратов, ул. Танкистов, 195</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>+7 (927) 279-09-83</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>term1998@yandex.ru</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>https://pkfterm.ru</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>+7 (927) 279-09-83 — в шапке и в блоке «Контактная информация»; term1998@yandex.ru — mailto и в блоке контактов. Одностраничный сайт — два места на одной страни</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://pkfterm.ru/#harakteristiki</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Регул»</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>+7 (499) 653-65-06</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>regyl21@mail.ru</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://regul21.ru</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>+7 (499) 653-65-06 и regyl21@mail.ru — в шапке, подвале и на «Контактах». Совпадает.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://regul21.ru/products/rybozashchitnye-ustrojstva</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -572,6 +1617,3551 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E153"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Таблица / № в ТЗ</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Позиция ТЗ</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Проверенных заводов</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Какие заводы</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1.1/14</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1.1/15</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1.1/16</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1.1/17</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1.1/18</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 40 Ру 16</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>1.1/19</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>1.3/101</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>1.3/102</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>1.3/103</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1.3/104</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>1.3/105</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1.5/4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1.5/5</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>1.5/6</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>1.5/7</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>1.5/8</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>1.6/51</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>1.6/52</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>1.6/53</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>1.6/54</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>1.6/55</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 40 Ру 16</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>1.6/56</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п1 Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «ТЕМПЕР»</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>1.3/39</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «Пензапромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>1.3/100</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Кран 11б27п(м) Ду 15 Ру 16 3-х ходовой для манометров</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «Пензапромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>1.6/16</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>1.6/50</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11б27п(м) Ду 015 Ру16 3-х ходовой для манометров</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>1.3/135</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой нержавеющий G1/2" муфтовый, полнопроходной, Ду 15 Ру 63</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — не закрыта: у проверенных заводов нет нерж. муфтового Ду15 на Ру63 — искать дополнительно</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>1.3/146</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый химический КШХ Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ЛЗТА «Маршал»</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>1.3/147</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый химический КШХ Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ЛЗТА «Маршал»</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>1.8/2</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 10нж45фт 2ЦФ Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ЛЗТА «Маршал»</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>1.8/3</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 10нж45фт 2ЦФ Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ЛЗТА «Маршал»</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>1.8/4</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 10нж45фт 2ЦФ Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ЛЗТА «Маршал»</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>1.1/20</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>1.1/21</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>1.2/1</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>1.2/2</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>1.2/3</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>1.2/4</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>1.2/5</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>1.3/106</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой фланцевый 11с22п Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>1.3/107</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой фланцевый 11с22п Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>1.3/108</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой фланцевый 11с22п Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>1.3/109</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11С67П Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>1.3/110</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11С67П Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>1.3/111</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11С67П Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>1.3/112</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11С67П Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>1.3/113</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>1.3/114</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>1.3/115</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>1.3/116</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>1.3/117</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>1.3/118</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>1.3/119</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>1.3/120</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>1.3/121</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>1.3/122</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>1.3/123</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>1.3/124</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>1.3/125</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>1.3/126</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>1.3/127</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>1.3/128</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>1.3/129</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>1.3/130</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>1.3/131</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>1.3/132</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>1.3/133</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>1.3/134</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>1.3/136</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>1.3/137</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>1.3/138</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>1.3/139</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>1.3/140</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>1.3/141</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>1.3/142</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>1.3/143</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>1.3/144</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>1.3/145</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>1.3/148</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>1.3/149</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>1.5/9</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>1.5/10</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>1.5/11</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>1.5/12</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>1.5/13</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>1.5/14</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>1.5/15</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>1.5/16</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>1.5/17</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>1.5/18</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>1.6/57</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 32 Ру 16</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>1.6/58</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>1.6/59</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>1.6/60</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>1.6/61</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>1.6/62</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>1.6/63</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Кран запорный шаровой 11С67П Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>1.6/64</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Кран запорный шаровой 11С67П Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>1.6/65</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Кран запорный шаровой 11С67П Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>1.6/66</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Кран запорный шаровой 11С67П Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>1.6/67</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Кран запорный шаровой 11С67П Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>1.6/68</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>1.6/69</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>1.6/70</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>1.6/71</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>1.6/72</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>1.6/73</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>1.6/74</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>1.6/75</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>1.6/76</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>1.6/77</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>1.6/78</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>1.6/79</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>1.6/80</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>1.6/81</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>1.6/82</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>1.6/83</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>1.6/84</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>1.6/85</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>1.6/86</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>1.6/87</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>1.6/88</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>1.7/2</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>1.7/3</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>1.7/4</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>1.8/5</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>1.8/6</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с22п Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>1.8/7</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд; ООО «АЛСО»; ООО «Краны Балашихи»; ЛЗТА «Маршал»; ООО «ТЕМПЕР»; РОБЕН</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>1.1/22</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>АО «УралТехКомплектация»; ООО «ПромАрм»; АО «Пензтяжпромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>1.1/23</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>АО «УралТехКомплектация»; ООО «ПромАрм»; АО «Пензтяжпромарматура»</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>1.3/32</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Клапан обратный фланцевый пружинный с аксиальным затвором NVD-402R Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — только частичный аналог (Гранлок RD16, не аксиальный) — согласовать эквивалент с заказчиком</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>1.3/33</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Клапан обратный фланцевый пружинный с аксиальным затвором NVD-402R Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — только частичный аналог (Гранлок RD16) — согласовать</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>1.3/34</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Клапан обратный фланцевый пружинный с аксиальным затвором NVD-402R Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — только частичный аналог (Гранлок RD16) — согласовать</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>1.3/150</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Затвор 32нж910р Ду 1000 Ру 10 с эл.приводом</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПромАрм»; АО «Пензтяжпромарматура» — точного аналога 32нж910р нет — исполнение (морская вода, КОФ, электропривод) согласовать с заводом</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>1.3/151</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный ЗДП-150-6,3-1-М-А-УХЛ1 (не под электропривод) Ду 150 Ру 6,3</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоПромАтомСервис»; ООО «Транс-Энерго» / ООО «Лидер-Энерго»</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>1.3/152</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный ЗДП-50-6,3-1-М-А-УХЛ1 Ду 50 Ру 6,3</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоПромАтомСервис»; ООО «Транс-Энерго» / ООО «Лидер-Энерго»</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>1.3/153</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный ЗДП-80-УХЛ1 Ду 80 Ру 6,3</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоПромАтомСервис»; ООО «Транс-Энерго» / ООО «Лидер-Энерго»</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>1.3/154</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 100, Ру 16</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>1.3/155</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>1.3/156</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>1.3/157</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>1.3/158</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>1.3/159</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>1.3/160</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>1.3/161</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>1.3/162</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Затвор поворотный дисковый Ду 65 Ру 16  ГРАНВЭЛ тип ЗПВС</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>1.6/89</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 100, Ру 16</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>1.6/90</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) ЗП ТЛ Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>1.6/91</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Затвор дисковый поворотный(ГРЭНВЭЛ) Тип /серия FL(w)-3-MR-E Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»; ОАО «Литейно-механический завод»; АО «УралТехКомплектация»; ООО «ПромАрм»</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Рыбозащитное устройство с потокообразователем</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПКФ «ТЕРМ»; ООО «Регул»</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Электропривод прямоходный Regada SТ0 490.0-00TQV/00</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация»; ООО «НПП «Промышленная автоматика»</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>1.6/93</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Электропривод Esbe 95 - 12051900</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация» — аналог ESBE — МЭОФ ЗЭиМ крупнее, проверить посадку на клапан</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E153"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -847,12 +5437,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
+      <c r="W4" s="7" t="n"/>
+      <c r="X4" s="7" t="n"/>
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -947,12 +5537,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
+      <c r="W5" s="7" t="n"/>
+      <c r="X5" s="7" t="n"/>
+      <c r="Y5" s="7" t="n"/>
+      <c r="Z5" s="7" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -1043,12 +5633,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="7" t="n"/>
+      <c r="W6" s="7" t="n"/>
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="7" t="n"/>
+      <c r="Z6" s="7" t="n"/>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -1143,12 +5733,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
+      <c r="W7" s="7" t="n"/>
+      <c r="X7" s="7" t="n"/>
+      <c r="Y7" s="7" t="n"/>
+      <c r="Z7" s="7" t="n"/>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -1239,12 +5829,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1339,12 +5929,12 @@
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -1439,12 +6029,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1539,12 +6129,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
+      <c r="Z11" s="7" t="n"/>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1635,12 +6225,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1735,12 +6325,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1835,12 +6425,12 @@
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
     </row>
     <row r="15" ht="75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1935,12 +6525,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
     </row>
     <row r="16" ht="75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -2039,12 +6629,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
     </row>
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -2135,12 +6725,12 @@
       </c>
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
     </row>
     <row r="18" ht="75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -2235,12 +6825,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -2335,12 +6925,12 @@
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
     </row>
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -2439,12 +7029,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -2543,12 +7133,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n"/>
+      <c r="Y21" s="7" t="n"/>
+      <c r="Z21" s="7" t="n"/>
     </row>
     <row r="22" ht="75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -2647,12 +7237,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n"/>
-      <c r="W22" s="4" t="n"/>
-      <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="4" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
+      <c r="W22" s="7" t="n"/>
+      <c r="X22" s="7" t="n"/>
+      <c r="Y22" s="7" t="n"/>
+      <c r="Z22" s="7" t="n"/>
     </row>
     <row r="23" ht="75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -2751,12 +7341,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U23" s="4" t="n"/>
-      <c r="V23" s="4" t="n"/>
-      <c r="W23" s="4" t="n"/>
-      <c r="X23" s="4" t="n"/>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="4" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
+      <c r="W23" s="7" t="n"/>
+      <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="7" t="n"/>
+      <c r="Z23" s="7" t="n"/>
     </row>
     <row r="24" ht="75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -2855,12 +7445,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U24" s="4" t="n"/>
-      <c r="V24" s="4" t="n"/>
-      <c r="W24" s="4" t="n"/>
-      <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="4" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="7" t="n"/>
+      <c r="X24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n"/>
+      <c r="Z24" s="7" t="n"/>
     </row>
     <row r="25" ht="75" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -2959,12 +7549,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U25" s="4" t="n"/>
-      <c r="V25" s="4" t="n"/>
-      <c r="W25" s="4" t="n"/>
-      <c r="X25" s="4" t="n"/>
-      <c r="Y25" s="4" t="n"/>
-      <c r="Z25" s="4" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
+      <c r="W25" s="7" t="n"/>
+      <c r="X25" s="7" t="n"/>
+      <c r="Y25" s="7" t="n"/>
+      <c r="Z25" s="7" t="n"/>
     </row>
     <row r="26" ht="75" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -3061,12 +7651,12 @@
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="4" t="n"/>
-      <c r="V26" s="4" t="n"/>
-      <c r="W26" s="4" t="n"/>
-      <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="4" t="n"/>
-      <c r="Z26" s="4" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="V26" s="7" t="n"/>
+      <c r="W26" s="7" t="n"/>
+      <c r="X26" s="7" t="n"/>
+      <c r="Y26" s="7" t="n"/>
+      <c r="Z26" s="7" t="n"/>
     </row>
     <row r="27" ht="75" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -3163,12 +7753,12 @@
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="4" t="n"/>
-      <c r="V27" s="4" t="n"/>
-      <c r="W27" s="4" t="n"/>
-      <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="4" t="n"/>
-      <c r="Z27" s="4" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
+      <c r="W27" s="7" t="n"/>
+      <c r="X27" s="7" t="n"/>
+      <c r="Y27" s="7" t="n"/>
+      <c r="Z27" s="7" t="n"/>
     </row>
     <row r="28" ht="75" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -3267,12 +7857,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U28" s="4" t="n"/>
-      <c r="V28" s="4" t="n"/>
-      <c r="W28" s="4" t="n"/>
-      <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n"/>
-      <c r="Z28" s="4" t="n"/>
+      <c r="U28" s="7" t="n"/>
+      <c r="V28" s="7" t="n"/>
+      <c r="W28" s="7" t="n"/>
+      <c r="X28" s="7" t="n"/>
+      <c r="Y28" s="7" t="n"/>
+      <c r="Z28" s="7" t="n"/>
     </row>
     <row r="29" ht="75" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -3371,12 +7961,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U29" s="4" t="n"/>
-      <c r="V29" s="4" t="n"/>
-      <c r="W29" s="4" t="n"/>
-      <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="4" t="n"/>
-      <c r="Z29" s="4" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
+      <c r="W29" s="7" t="n"/>
+      <c r="X29" s="7" t="n"/>
+      <c r="Y29" s="7" t="n"/>
+      <c r="Z29" s="7" t="n"/>
     </row>
     <row r="30" ht="75" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -3467,12 +8057,12 @@
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="4" t="n"/>
-      <c r="V30" s="4" t="n"/>
-      <c r="W30" s="4" t="n"/>
-      <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="4" t="n"/>
-      <c r="Z30" s="4" t="n"/>
+      <c r="U30" s="7" t="n"/>
+      <c r="V30" s="7" t="n"/>
+      <c r="W30" s="7" t="n"/>
+      <c r="X30" s="7" t="n"/>
+      <c r="Y30" s="7" t="n"/>
+      <c r="Z30" s="7" t="n"/>
     </row>
     <row r="31" ht="75" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -3567,12 +8157,12 @@
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr"/>
-      <c r="U31" s="4" t="n"/>
-      <c r="V31" s="4" t="n"/>
-      <c r="W31" s="4" t="n"/>
-      <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n"/>
-      <c r="Z31" s="4" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
+      <c r="W31" s="7" t="n"/>
+      <c r="X31" s="7" t="n"/>
+      <c r="Y31" s="7" t="n"/>
+      <c r="Z31" s="7" t="n"/>
     </row>
     <row r="32" ht="75" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -3667,12 +8257,12 @@
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="4" t="n"/>
-      <c r="V32" s="4" t="n"/>
-      <c r="W32" s="4" t="n"/>
-      <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="4" t="n"/>
-      <c r="Z32" s="4" t="n"/>
+      <c r="U32" s="7" t="n"/>
+      <c r="V32" s="7" t="n"/>
+      <c r="W32" s="7" t="n"/>
+      <c r="X32" s="7" t="n"/>
+      <c r="Y32" s="7" t="n"/>
+      <c r="Z32" s="7" t="n"/>
     </row>
     <row r="33" ht="75" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -3763,12 +8353,12 @@
       </c>
       <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="4" t="n"/>
-      <c r="V33" s="4" t="n"/>
-      <c r="W33" s="4" t="n"/>
-      <c r="X33" s="4" t="n"/>
-      <c r="Y33" s="4" t="n"/>
-      <c r="Z33" s="4" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
+      <c r="W33" s="7" t="n"/>
+      <c r="X33" s="7" t="n"/>
+      <c r="Y33" s="7" t="n"/>
+      <c r="Z33" s="7" t="n"/>
     </row>
     <row r="34" ht="75" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -3859,12 +8449,12 @@
       </c>
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="4" t="n"/>
-      <c r="V34" s="4" t="n"/>
-      <c r="W34" s="4" t="n"/>
-      <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
-      <c r="Z34" s="4" t="n"/>
+      <c r="U34" s="7" t="n"/>
+      <c r="V34" s="7" t="n"/>
+      <c r="W34" s="7" t="n"/>
+      <c r="X34" s="7" t="n"/>
+      <c r="Y34" s="7" t="n"/>
+      <c r="Z34" s="7" t="n"/>
     </row>
     <row r="35" ht="75" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -3955,12 +8545,12 @@
       </c>
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="4" t="n"/>
-      <c r="V35" s="4" t="n"/>
-      <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n"/>
-      <c r="Y35" s="4" t="n"/>
-      <c r="Z35" s="4" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
+      <c r="W35" s="7" t="n"/>
+      <c r="X35" s="7" t="n"/>
+      <c r="Y35" s="7" t="n"/>
+      <c r="Z35" s="7" t="n"/>
     </row>
     <row r="36" ht="75" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -4059,12 +8649,12 @@
           <t>Класс герметичности по ГОСТ 9544-2015 «А»</t>
         </is>
       </c>
-      <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n"/>
-      <c r="W36" s="4" t="n"/>
-      <c r="X36" s="4" t="n"/>
-      <c r="Y36" s="4" t="n"/>
-      <c r="Z36" s="4" t="n"/>
+      <c r="U36" s="7" t="n"/>
+      <c r="V36" s="7" t="n"/>
+      <c r="W36" s="7" t="n"/>
+      <c r="X36" s="7" t="n"/>
+      <c r="Y36" s="7" t="n"/>
+      <c r="Z36" s="7" t="n"/>
     </row>
     <row r="37" ht="75" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -4161,12 +8751,12 @@
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="4" t="n"/>
-      <c r="V37" s="4" t="n"/>
-      <c r="W37" s="4" t="n"/>
-      <c r="X37" s="4" t="n"/>
-      <c r="Y37" s="4" t="n"/>
-      <c r="Z37" s="4" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
+      <c r="W37" s="7" t="n"/>
+      <c r="X37" s="7" t="n"/>
+      <c r="Y37" s="7" t="n"/>
+      <c r="Z37" s="7" t="n"/>
     </row>
     <row r="38" ht="75" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -4265,12 +8855,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U38" s="4" t="n"/>
-      <c r="V38" s="4" t="n"/>
-      <c r="W38" s="4" t="n"/>
-      <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="4" t="n"/>
-      <c r="Z38" s="4" t="n"/>
+      <c r="U38" s="7" t="n"/>
+      <c r="V38" s="7" t="n"/>
+      <c r="W38" s="7" t="n"/>
+      <c r="X38" s="7" t="n"/>
+      <c r="Y38" s="7" t="n"/>
+      <c r="Z38" s="7" t="n"/>
     </row>
     <row r="39" ht="75" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -4365,12 +8955,12 @@
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="4" t="n"/>
-      <c r="V39" s="4" t="n"/>
-      <c r="W39" s="4" t="n"/>
-      <c r="X39" s="4" t="n"/>
-      <c r="Y39" s="4" t="n"/>
-      <c r="Z39" s="4" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
+      <c r="W39" s="7" t="n"/>
+      <c r="X39" s="7" t="n"/>
+      <c r="Y39" s="7" t="n"/>
+      <c r="Z39" s="7" t="n"/>
     </row>
     <row r="40" ht="75" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -4465,12 +9055,12 @@
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="4" t="n"/>
-      <c r="V40" s="4" t="n"/>
-      <c r="W40" s="4" t="n"/>
-      <c r="X40" s="4" t="n"/>
-      <c r="Y40" s="4" t="n"/>
-      <c r="Z40" s="4" t="n"/>
+      <c r="U40" s="7" t="n"/>
+      <c r="V40" s="7" t="n"/>
+      <c r="W40" s="7" t="n"/>
+      <c r="X40" s="7" t="n"/>
+      <c r="Y40" s="7" t="n"/>
+      <c r="Z40" s="7" t="n"/>
     </row>
     <row r="41" ht="75" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -4565,12 +9155,12 @@
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n"/>
-      <c r="W41" s="4" t="n"/>
-      <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="4" t="n"/>
-      <c r="Z41" s="4" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
+      <c r="W41" s="7" t="n"/>
+      <c r="X41" s="7" t="n"/>
+      <c r="Y41" s="7" t="n"/>
+      <c r="Z41" s="7" t="n"/>
     </row>
     <row r="42" ht="75" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -4670,12 +9260,12 @@
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="4" t="n"/>
-      <c r="V42" s="4" t="n"/>
-      <c r="W42" s="4" t="n"/>
-      <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="4" t="n"/>
-      <c r="Z42" s="4" t="n"/>
+      <c r="U42" s="7" t="n"/>
+      <c r="V42" s="7" t="n"/>
+      <c r="W42" s="7" t="n"/>
+      <c r="X42" s="7" t="n"/>
+      <c r="Y42" s="7" t="n"/>
+      <c r="Z42" s="7" t="n"/>
     </row>
     <row r="43" ht="75" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -4774,12 +9364,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U43" s="4" t="n"/>
-      <c r="V43" s="4" t="n"/>
-      <c r="W43" s="4" t="n"/>
-      <c r="X43" s="4" t="n"/>
-      <c r="Y43" s="4" t="n"/>
-      <c r="Z43" s="4" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
+      <c r="W43" s="7" t="n"/>
+      <c r="X43" s="7" t="n"/>
+      <c r="Y43" s="7" t="n"/>
+      <c r="Z43" s="7" t="n"/>
     </row>
     <row r="44" ht="75" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -4878,12 +9468,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U44" s="4" t="n"/>
-      <c r="V44" s="4" t="n"/>
-      <c r="W44" s="4" t="n"/>
-      <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="4" t="n"/>
-      <c r="Z44" s="4" t="n"/>
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="7" t="n"/>
+      <c r="W44" s="7" t="n"/>
+      <c r="X44" s="7" t="n"/>
+      <c r="Y44" s="7" t="n"/>
+      <c r="Z44" s="7" t="n"/>
     </row>
     <row r="45" ht="75" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -4982,12 +9572,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U45" s="4" t="n"/>
-      <c r="V45" s="4" t="n"/>
-      <c r="W45" s="4" t="n"/>
-      <c r="X45" s="4" t="n"/>
-      <c r="Y45" s="4" t="n"/>
-      <c r="Z45" s="4" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
+      <c r="W45" s="7" t="n"/>
+      <c r="X45" s="7" t="n"/>
+      <c r="Y45" s="7" t="n"/>
+      <c r="Z45" s="7" t="n"/>
     </row>
     <row r="46" ht="75" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -5082,12 +9672,12 @@
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="4" t="n"/>
-      <c r="V46" s="4" t="n"/>
-      <c r="W46" s="4" t="n"/>
-      <c r="X46" s="4" t="n"/>
-      <c r="Y46" s="4" t="n"/>
-      <c r="Z46" s="4" t="n"/>
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="7" t="n"/>
+      <c r="W46" s="7" t="n"/>
+      <c r="X46" s="7" t="n"/>
+      <c r="Y46" s="7" t="n"/>
+      <c r="Z46" s="7" t="n"/>
     </row>
     <row r="47" ht="75" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -5182,12 +9772,12 @@
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="4" t="n"/>
-      <c r="V47" s="4" t="n"/>
-      <c r="W47" s="4" t="n"/>
-      <c r="X47" s="4" t="n"/>
-      <c r="Y47" s="4" t="n"/>
-      <c r="Z47" s="4" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
+      <c r="W47" s="7" t="n"/>
+      <c r="X47" s="7" t="n"/>
+      <c r="Y47" s="7" t="n"/>
+      <c r="Z47" s="7" t="n"/>
     </row>
     <row r="48" ht="75" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -5282,12 +9872,12 @@
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="4" t="n"/>
-      <c r="V48" s="4" t="n"/>
-      <c r="W48" s="4" t="n"/>
-      <c r="X48" s="4" t="n"/>
-      <c r="Y48" s="4" t="n"/>
-      <c r="Z48" s="4" t="n"/>
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="7" t="n"/>
+      <c r="W48" s="7" t="n"/>
+      <c r="X48" s="7" t="n"/>
+      <c r="Y48" s="7" t="n"/>
+      <c r="Z48" s="7" t="n"/>
     </row>
     <row r="49" ht="75" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -5382,12 +9972,12 @@
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="4" t="n"/>
-      <c r="V49" s="4" t="n"/>
-      <c r="W49" s="4" t="n"/>
-      <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="4" t="n"/>
-      <c r="Z49" s="4" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
+      <c r="W49" s="7" t="n"/>
+      <c r="X49" s="7" t="n"/>
+      <c r="Y49" s="7" t="n"/>
+      <c r="Z49" s="7" t="n"/>
     </row>
     <row r="50" ht="75" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -5481,12 +10071,12 @@
       </c>
       <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n"/>
-      <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n"/>
-      <c r="Z50" s="4" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
+      <c r="W50" s="7" t="n"/>
+      <c r="X50" s="7" t="n"/>
+      <c r="Y50" s="7" t="n"/>
+      <c r="Z50" s="7" t="n"/>
     </row>
     <row r="51" ht="75" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -5573,12 +10163,12 @@
       </c>
       <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="4" t="n"/>
-      <c r="V51" s="4" t="n"/>
-      <c r="W51" s="4" t="n"/>
-      <c r="X51" s="4" t="n"/>
-      <c r="Y51" s="4" t="n"/>
-      <c r="Z51" s="4" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
+      <c r="W51" s="7" t="n"/>
+      <c r="X51" s="7" t="n"/>
+      <c r="Y51" s="7" t="n"/>
+      <c r="Z51" s="7" t="n"/>
     </row>
     <row r="52" ht="75" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -5673,12 +10263,12 @@
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="4" t="n"/>
-      <c r="V52" s="4" t="n"/>
-      <c r="W52" s="4" t="n"/>
-      <c r="X52" s="4" t="n"/>
-      <c r="Y52" s="4" t="n"/>
-      <c r="Z52" s="4" t="n"/>
+      <c r="U52" s="7" t="n"/>
+      <c r="V52" s="7" t="n"/>
+      <c r="W52" s="7" t="n"/>
+      <c r="X52" s="7" t="n"/>
+      <c r="Y52" s="7" t="n"/>
+      <c r="Z52" s="7" t="n"/>
     </row>
     <row r="53" ht="75" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -5772,12 +10362,12 @@
       </c>
       <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="4" t="n"/>
-      <c r="V53" s="4" t="n"/>
-      <c r="W53" s="4" t="n"/>
-      <c r="X53" s="4" t="n"/>
-      <c r="Y53" s="4" t="n"/>
-      <c r="Z53" s="4" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
+      <c r="W53" s="7" t="n"/>
+      <c r="X53" s="7" t="n"/>
+      <c r="Y53" s="7" t="n"/>
+      <c r="Z53" s="7" t="n"/>
     </row>
     <row r="54" ht="75" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -5872,12 +10462,12 @@
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="4" t="n"/>
-      <c r="V54" s="4" t="n"/>
-      <c r="W54" s="4" t="n"/>
-      <c r="X54" s="4" t="n"/>
-      <c r="Y54" s="4" t="n"/>
-      <c r="Z54" s="4" t="n"/>
+      <c r="U54" s="7" t="n"/>
+      <c r="V54" s="7" t="n"/>
+      <c r="W54" s="7" t="n"/>
+      <c r="X54" s="7" t="n"/>
+      <c r="Y54" s="7" t="n"/>
+      <c r="Z54" s="7" t="n"/>
     </row>
     <row r="55" ht="75" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -5972,12 +10562,12 @@
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="4" t="n"/>
-      <c r="V55" s="4" t="n"/>
-      <c r="W55" s="4" t="n"/>
-      <c r="X55" s="4" t="n"/>
-      <c r="Y55" s="4" t="n"/>
-      <c r="Z55" s="4" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
+      <c r="W55" s="7" t="n"/>
+      <c r="X55" s="7" t="n"/>
+      <c r="Y55" s="7" t="n"/>
+      <c r="Z55" s="7" t="n"/>
     </row>
     <row r="56" ht="75" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -6072,12 +10662,12 @@
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="4" t="n"/>
-      <c r="V56" s="4" t="n"/>
-      <c r="W56" s="4" t="n"/>
-      <c r="X56" s="4" t="n"/>
-      <c r="Y56" s="4" t="n"/>
-      <c r="Z56" s="4" t="n"/>
+      <c r="U56" s="7" t="n"/>
+      <c r="V56" s="7" t="n"/>
+      <c r="W56" s="7" t="n"/>
+      <c r="X56" s="7" t="n"/>
+      <c r="Y56" s="7" t="n"/>
+      <c r="Z56" s="7" t="n"/>
     </row>
     <row r="57" ht="75" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -6172,12 +10762,12 @@
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="4" t="n"/>
-      <c r="V57" s="4" t="n"/>
-      <c r="W57" s="4" t="n"/>
-      <c r="X57" s="4" t="n"/>
-      <c r="Y57" s="4" t="n"/>
-      <c r="Z57" s="4" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
+      <c r="W57" s="7" t="n"/>
+      <c r="X57" s="7" t="n"/>
+      <c r="Y57" s="7" t="n"/>
+      <c r="Z57" s="7" t="n"/>
     </row>
     <row r="58" ht="75" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -6272,12 +10862,12 @@
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="4" t="n"/>
-      <c r="V58" s="4" t="n"/>
-      <c r="W58" s="4" t="n"/>
-      <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="4" t="n"/>
-      <c r="Z58" s="4" t="n"/>
+      <c r="U58" s="7" t="n"/>
+      <c r="V58" s="7" t="n"/>
+      <c r="W58" s="7" t="n"/>
+      <c r="X58" s="7" t="n"/>
+      <c r="Y58" s="7" t="n"/>
+      <c r="Z58" s="7" t="n"/>
     </row>
     <row r="59" ht="75" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -6372,12 +10962,12 @@
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="4" t="n"/>
-      <c r="V59" s="4" t="n"/>
-      <c r="W59" s="4" t="n"/>
-      <c r="X59" s="4" t="n"/>
-      <c r="Y59" s="4" t="n"/>
-      <c r="Z59" s="4" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
+      <c r="W59" s="7" t="n"/>
+      <c r="X59" s="7" t="n"/>
+      <c r="Y59" s="7" t="n"/>
+      <c r="Z59" s="7" t="n"/>
     </row>
     <row r="60" ht="75" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -6472,12 +11062,12 @@
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="4" t="n"/>
-      <c r="V60" s="4" t="n"/>
-      <c r="W60" s="4" t="n"/>
-      <c r="X60" s="4" t="n"/>
-      <c r="Y60" s="4" t="n"/>
-      <c r="Z60" s="4" t="n"/>
+      <c r="U60" s="7" t="n"/>
+      <c r="V60" s="7" t="n"/>
+      <c r="W60" s="7" t="n"/>
+      <c r="X60" s="7" t="n"/>
+      <c r="Y60" s="7" t="n"/>
+      <c r="Z60" s="7" t="n"/>
     </row>
     <row r="61" ht="75" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -6572,12 +11162,12 @@
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="4" t="n"/>
-      <c r="V61" s="4" t="n"/>
-      <c r="W61" s="4" t="n"/>
-      <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="4" t="n"/>
-      <c r="Z61" s="4" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
+      <c r="W61" s="7" t="n"/>
+      <c r="X61" s="7" t="n"/>
+      <c r="Y61" s="7" t="n"/>
+      <c r="Z61" s="7" t="n"/>
     </row>
     <row r="62" ht="75" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -6672,12 +11262,12 @@
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="4" t="n"/>
-      <c r="V62" s="4" t="n"/>
-      <c r="W62" s="4" t="n"/>
-      <c r="X62" s="4" t="n"/>
-      <c r="Y62" s="4" t="n"/>
-      <c r="Z62" s="4" t="n"/>
+      <c r="U62" s="7" t="n"/>
+      <c r="V62" s="7" t="n"/>
+      <c r="W62" s="7" t="n"/>
+      <c r="X62" s="7" t="n"/>
+      <c r="Y62" s="7" t="n"/>
+      <c r="Z62" s="7" t="n"/>
     </row>
     <row r="63" ht="75" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -6772,12 +11362,12 @@
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="4" t="n"/>
-      <c r="V63" s="4" t="n"/>
-      <c r="W63" s="4" t="n"/>
-      <c r="X63" s="4" t="n"/>
-      <c r="Y63" s="4" t="n"/>
-      <c r="Z63" s="4" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
+      <c r="W63" s="7" t="n"/>
+      <c r="X63" s="7" t="n"/>
+      <c r="Y63" s="7" t="n"/>
+      <c r="Z63" s="7" t="n"/>
     </row>
     <row r="64" ht="75" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -6877,12 +11467,12 @@
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="4" t="n"/>
-      <c r="V64" s="4" t="n"/>
-      <c r="W64" s="4" t="n"/>
-      <c r="X64" s="4" t="n"/>
-      <c r="Y64" s="4" t="n"/>
-      <c r="Z64" s="4" t="n"/>
+      <c r="U64" s="7" t="n"/>
+      <c r="V64" s="7" t="n"/>
+      <c r="W64" s="7" t="n"/>
+      <c r="X64" s="7" t="n"/>
+      <c r="Y64" s="7" t="n"/>
+      <c r="Z64" s="7" t="n"/>
     </row>
     <row r="65" ht="75" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -6982,12 +11572,12 @@
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr"/>
-      <c r="U65" s="4" t="n"/>
-      <c r="V65" s="4" t="n"/>
-      <c r="W65" s="4" t="n"/>
-      <c r="X65" s="4" t="n"/>
-      <c r="Y65" s="4" t="n"/>
-      <c r="Z65" s="4" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
+      <c r="W65" s="7" t="n"/>
+      <c r="X65" s="7" t="n"/>
+      <c r="Y65" s="7" t="n"/>
+      <c r="Z65" s="7" t="n"/>
     </row>
     <row r="66" ht="75" customHeight="1">
       <c r="A66" s="3" t="n">
@@ -7087,12 +11677,12 @@
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr"/>
-      <c r="U66" s="4" t="n"/>
-      <c r="V66" s="4" t="n"/>
-      <c r="W66" s="4" t="n"/>
-      <c r="X66" s="4" t="n"/>
-      <c r="Y66" s="4" t="n"/>
-      <c r="Z66" s="4" t="n"/>
+      <c r="U66" s="7" t="n"/>
+      <c r="V66" s="7" t="n"/>
+      <c r="W66" s="7" t="n"/>
+      <c r="X66" s="7" t="n"/>
+      <c r="Y66" s="7" t="n"/>
+      <c r="Z66" s="7" t="n"/>
     </row>
     <row r="67" ht="75" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -7192,12 +11782,12 @@
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr"/>
-      <c r="U67" s="4" t="n"/>
-      <c r="V67" s="4" t="n"/>
-      <c r="W67" s="4" t="n"/>
-      <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="4" t="n"/>
-      <c r="Z67" s="4" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
+      <c r="W67" s="7" t="n"/>
+      <c r="X67" s="7" t="n"/>
+      <c r="Y67" s="7" t="n"/>
+      <c r="Z67" s="7" t="n"/>
     </row>
     <row r="68" ht="75" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -7288,12 +11878,12 @@
       </c>
       <c r="S68" s="3" t="inlineStr"/>
       <c r="T68" s="3" t="inlineStr"/>
-      <c r="U68" s="4" t="n"/>
-      <c r="V68" s="4" t="n"/>
-      <c r="W68" s="4" t="n"/>
-      <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="4" t="n"/>
-      <c r="Z68" s="4" t="n"/>
+      <c r="U68" s="7" t="n"/>
+      <c r="V68" s="7" t="n"/>
+      <c r="W68" s="7" t="n"/>
+      <c r="X68" s="7" t="n"/>
+      <c r="Y68" s="7" t="n"/>
+      <c r="Z68" s="7" t="n"/>
     </row>
     <row r="69" ht="75" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -7384,12 +11974,12 @@
       </c>
       <c r="S69" s="3" t="inlineStr"/>
       <c r="T69" s="3" t="inlineStr"/>
-      <c r="U69" s="4" t="n"/>
-      <c r="V69" s="4" t="n"/>
-      <c r="W69" s="4" t="n"/>
-      <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="4" t="n"/>
-      <c r="Z69" s="4" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
+      <c r="W69" s="7" t="n"/>
+      <c r="X69" s="7" t="n"/>
+      <c r="Y69" s="7" t="n"/>
+      <c r="Z69" s="7" t="n"/>
     </row>
     <row r="70" ht="75" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -7480,12 +12070,12 @@
       </c>
       <c r="S70" s="3" t="inlineStr"/>
       <c r="T70" s="3" t="inlineStr"/>
-      <c r="U70" s="4" t="n"/>
-      <c r="V70" s="4" t="n"/>
-      <c r="W70" s="4" t="n"/>
-      <c r="X70" s="4" t="n"/>
-      <c r="Y70" s="4" t="n"/>
-      <c r="Z70" s="4" t="n"/>
+      <c r="U70" s="7" t="n"/>
+      <c r="V70" s="7" t="n"/>
+      <c r="W70" s="7" t="n"/>
+      <c r="X70" s="7" t="n"/>
+      <c r="Y70" s="7" t="n"/>
+      <c r="Z70" s="7" t="n"/>
     </row>
     <row r="71" ht="75" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -7576,12 +12166,12 @@
       </c>
       <c r="S71" s="3" t="inlineStr"/>
       <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="4" t="n"/>
-      <c r="V71" s="4" t="n"/>
-      <c r="W71" s="4" t="n"/>
-      <c r="X71" s="4" t="n"/>
-      <c r="Y71" s="4" t="n"/>
-      <c r="Z71" s="4" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
+      <c r="W71" s="7" t="n"/>
+      <c r="X71" s="7" t="n"/>
+      <c r="Y71" s="7" t="n"/>
+      <c r="Z71" s="7" t="n"/>
     </row>
     <row r="72" ht="75" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -7672,12 +12262,12 @@
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr"/>
-      <c r="U72" s="4" t="n"/>
-      <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="n"/>
-      <c r="X72" s="4" t="n"/>
-      <c r="Y72" s="4" t="n"/>
-      <c r="Z72" s="4" t="n"/>
+      <c r="U72" s="7" t="n"/>
+      <c r="V72" s="7" t="n"/>
+      <c r="W72" s="7" t="n"/>
+      <c r="X72" s="7" t="n"/>
+      <c r="Y72" s="7" t="n"/>
+      <c r="Z72" s="7" t="n"/>
     </row>
     <row r="73" ht="75" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -7772,12 +12362,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U73" s="4" t="n"/>
-      <c r="V73" s="4" t="n"/>
-      <c r="W73" s="4" t="n"/>
-      <c r="X73" s="4" t="n"/>
-      <c r="Y73" s="4" t="n"/>
-      <c r="Z73" s="4" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
+      <c r="W73" s="7" t="n"/>
+      <c r="X73" s="7" t="n"/>
+      <c r="Y73" s="7" t="n"/>
+      <c r="Z73" s="7" t="n"/>
     </row>
     <row r="74" ht="75" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -7872,12 +12462,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n"/>
-      <c r="W74" s="4" t="n"/>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n"/>
-      <c r="Z74" s="4" t="n"/>
+      <c r="U74" s="7" t="n"/>
+      <c r="V74" s="7" t="n"/>
+      <c r="W74" s="7" t="n"/>
+      <c r="X74" s="7" t="n"/>
+      <c r="Y74" s="7" t="n"/>
+      <c r="Z74" s="7" t="n"/>
     </row>
     <row r="75" ht="75" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -7972,12 +12562,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U75" s="4" t="n"/>
-      <c r="V75" s="4" t="n"/>
-      <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="n"/>
-      <c r="Z75" s="4" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
+      <c r="W75" s="7" t="n"/>
+      <c r="X75" s="7" t="n"/>
+      <c r="Y75" s="7" t="n"/>
+      <c r="Z75" s="7" t="n"/>
     </row>
     <row r="76" ht="75" customHeight="1">
       <c r="A76" s="3" t="n">
@@ -8068,12 +12658,12 @@
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr"/>
-      <c r="U76" s="4" t="n"/>
-      <c r="V76" s="4" t="n"/>
-      <c r="W76" s="4" t="n"/>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="4" t="n"/>
-      <c r="Z76" s="4" t="n"/>
+      <c r="U76" s="7" t="n"/>
+      <c r="V76" s="7" t="n"/>
+      <c r="W76" s="7" t="n"/>
+      <c r="X76" s="7" t="n"/>
+      <c r="Y76" s="7" t="n"/>
+      <c r="Z76" s="7" t="n"/>
     </row>
     <row r="77" ht="75" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -8164,12 +12754,12 @@
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr"/>
-      <c r="U77" s="4" t="n"/>
-      <c r="V77" s="4" t="n"/>
-      <c r="W77" s="4" t="n"/>
-      <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="4" t="n"/>
-      <c r="Z77" s="4" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
+      <c r="W77" s="7" t="n"/>
+      <c r="X77" s="7" t="n"/>
+      <c r="Y77" s="7" t="n"/>
+      <c r="Z77" s="7" t="n"/>
     </row>
     <row r="78" ht="75" customHeight="1">
       <c r="A78" s="3" t="n">
@@ -8260,12 +12850,12 @@
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr"/>
-      <c r="U78" s="4" t="n"/>
-      <c r="V78" s="4" t="n"/>
-      <c r="W78" s="4" t="n"/>
-      <c r="X78" s="4" t="n"/>
-      <c r="Y78" s="4" t="n"/>
-      <c r="Z78" s="4" t="n"/>
+      <c r="U78" s="7" t="n"/>
+      <c r="V78" s="7" t="n"/>
+      <c r="W78" s="7" t="n"/>
+      <c r="X78" s="7" t="n"/>
+      <c r="Y78" s="7" t="n"/>
+      <c r="Z78" s="7" t="n"/>
     </row>
     <row r="79" ht="75" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -8356,12 +12946,12 @@
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr"/>
-      <c r="U79" s="4" t="n"/>
-      <c r="V79" s="4" t="n"/>
-      <c r="W79" s="4" t="n"/>
-      <c r="X79" s="4" t="n"/>
-      <c r="Y79" s="4" t="n"/>
-      <c r="Z79" s="4" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
+      <c r="W79" s="7" t="n"/>
+      <c r="X79" s="7" t="n"/>
+      <c r="Y79" s="7" t="n"/>
+      <c r="Z79" s="7" t="n"/>
     </row>
     <row r="80" ht="75" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -8452,12 +13042,12 @@
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr"/>
-      <c r="U80" s="4" t="n"/>
-      <c r="V80" s="4" t="n"/>
-      <c r="W80" s="4" t="n"/>
-      <c r="X80" s="4" t="n"/>
-      <c r="Y80" s="4" t="n"/>
-      <c r="Z80" s="4" t="n"/>
+      <c r="U80" s="7" t="n"/>
+      <c r="V80" s="7" t="n"/>
+      <c r="W80" s="7" t="n"/>
+      <c r="X80" s="7" t="n"/>
+      <c r="Y80" s="7" t="n"/>
+      <c r="Z80" s="7" t="n"/>
     </row>
     <row r="81" ht="75" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -8548,12 +13138,12 @@
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr"/>
-      <c r="U81" s="4" t="n"/>
-      <c r="V81" s="4" t="n"/>
-      <c r="W81" s="4" t="n"/>
-      <c r="X81" s="4" t="n"/>
-      <c r="Y81" s="4" t="n"/>
-      <c r="Z81" s="4" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
+      <c r="W81" s="7" t="n"/>
+      <c r="X81" s="7" t="n"/>
+      <c r="Y81" s="7" t="n"/>
+      <c r="Z81" s="7" t="n"/>
     </row>
     <row r="82" ht="75" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -8644,12 +13234,12 @@
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr"/>
-      <c r="U82" s="4" t="n"/>
-      <c r="V82" s="4" t="n"/>
-      <c r="W82" s="4" t="n"/>
-      <c r="X82" s="4" t="n"/>
-      <c r="Y82" s="4" t="n"/>
-      <c r="Z82" s="4" t="n"/>
+      <c r="U82" s="7" t="n"/>
+      <c r="V82" s="7" t="n"/>
+      <c r="W82" s="7" t="n"/>
+      <c r="X82" s="7" t="n"/>
+      <c r="Y82" s="7" t="n"/>
+      <c r="Z82" s="7" t="n"/>
     </row>
     <row r="83" ht="75" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -8736,12 +13326,12 @@
         </is>
       </c>
       <c r="T83" s="3" t="inlineStr"/>
-      <c r="U83" s="4" t="n"/>
-      <c r="V83" s="4" t="n"/>
-      <c r="W83" s="4" t="n"/>
-      <c r="X83" s="4" t="n"/>
-      <c r="Y83" s="4" t="n"/>
-      <c r="Z83" s="4" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
+      <c r="W83" s="7" t="n"/>
+      <c r="X83" s="7" t="n"/>
+      <c r="Y83" s="7" t="n"/>
+      <c r="Z83" s="7" t="n"/>
     </row>
     <row r="84" ht="75" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -8840,12 +13430,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U84" s="4" t="n"/>
-      <c r="V84" s="4" t="n"/>
-      <c r="W84" s="4" t="n"/>
-      <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
-      <c r="Z84" s="4" t="n"/>
+      <c r="U84" s="7" t="n"/>
+      <c r="V84" s="7" t="n"/>
+      <c r="W84" s="7" t="n"/>
+      <c r="X84" s="7" t="n"/>
+      <c r="Y84" s="7" t="n"/>
+      <c r="Z84" s="7" t="n"/>
     </row>
     <row r="85" ht="75" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -8944,12 +13534,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U85" s="4" t="n"/>
-      <c r="V85" s="4" t="n"/>
-      <c r="W85" s="4" t="n"/>
-      <c r="X85" s="4" t="n"/>
-      <c r="Y85" s="4" t="n"/>
-      <c r="Z85" s="4" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
+      <c r="W85" s="7" t="n"/>
+      <c r="X85" s="7" t="n"/>
+      <c r="Y85" s="7" t="n"/>
+      <c r="Z85" s="7" t="n"/>
     </row>
     <row r="86" ht="75" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -9048,12 +13638,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U86" s="4" t="n"/>
-      <c r="V86" s="4" t="n"/>
-      <c r="W86" s="4" t="n"/>
-      <c r="X86" s="4" t="n"/>
-      <c r="Y86" s="4" t="n"/>
-      <c r="Z86" s="4" t="n"/>
+      <c r="U86" s="7" t="n"/>
+      <c r="V86" s="7" t="n"/>
+      <c r="W86" s="7" t="n"/>
+      <c r="X86" s="7" t="n"/>
+      <c r="Y86" s="7" t="n"/>
+      <c r="Z86" s="7" t="n"/>
     </row>
     <row r="87" ht="75" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -9147,12 +13737,12 @@
       </c>
       <c r="S87" s="3" t="inlineStr"/>
       <c r="T87" s="3" t="inlineStr"/>
-      <c r="U87" s="4" t="n"/>
-      <c r="V87" s="4" t="n"/>
-      <c r="W87" s="4" t="n"/>
-      <c r="X87" s="4" t="n"/>
-      <c r="Y87" s="4" t="n"/>
-      <c r="Z87" s="4" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
+      <c r="W87" s="7" t="n"/>
+      <c r="X87" s="7" t="n"/>
+      <c r="Y87" s="7" t="n"/>
+      <c r="Z87" s="7" t="n"/>
     </row>
     <row r="88" ht="75" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -9239,12 +13829,12 @@
       </c>
       <c r="S88" s="3" t="inlineStr"/>
       <c r="T88" s="3" t="inlineStr"/>
-      <c r="U88" s="4" t="n"/>
-      <c r="V88" s="4" t="n"/>
-      <c r="W88" s="4" t="n"/>
-      <c r="X88" s="4" t="n"/>
-      <c r="Y88" s="4" t="n"/>
-      <c r="Z88" s="4" t="n"/>
+      <c r="U88" s="7" t="n"/>
+      <c r="V88" s="7" t="n"/>
+      <c r="W88" s="7" t="n"/>
+      <c r="X88" s="7" t="n"/>
+      <c r="Y88" s="7" t="n"/>
+      <c r="Z88" s="7" t="n"/>
     </row>
     <row r="89" ht="75" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -9339,12 +13929,12 @@
         </is>
       </c>
       <c r="T89" s="3" t="inlineStr"/>
-      <c r="U89" s="4" t="n"/>
-      <c r="V89" s="4" t="n"/>
-      <c r="W89" s="4" t="n"/>
-      <c r="X89" s="4" t="n"/>
-      <c r="Y89" s="4" t="n"/>
-      <c r="Z89" s="4" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
+      <c r="W89" s="7" t="n"/>
+      <c r="X89" s="7" t="n"/>
+      <c r="Y89" s="7" t="n"/>
+      <c r="Z89" s="7" t="n"/>
     </row>
     <row r="90" ht="75" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -9438,12 +14028,12 @@
       </c>
       <c r="S90" s="3" t="inlineStr"/>
       <c r="T90" s="3" t="inlineStr"/>
-      <c r="U90" s="4" t="n"/>
-      <c r="V90" s="4" t="n"/>
-      <c r="W90" s="4" t="n"/>
-      <c r="X90" s="4" t="n"/>
-      <c r="Y90" s="4" t="n"/>
-      <c r="Z90" s="4" t="n"/>
+      <c r="U90" s="7" t="n"/>
+      <c r="V90" s="7" t="n"/>
+      <c r="W90" s="7" t="n"/>
+      <c r="X90" s="7" t="n"/>
+      <c r="Y90" s="7" t="n"/>
+      <c r="Z90" s="7" t="n"/>
     </row>
     <row r="91" ht="75" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -9538,12 +14128,12 @@
         </is>
       </c>
       <c r="T91" s="3" t="inlineStr"/>
-      <c r="U91" s="4" t="n"/>
-      <c r="V91" s="4" t="n"/>
-      <c r="W91" s="4" t="n"/>
-      <c r="X91" s="4" t="n"/>
-      <c r="Y91" s="4" t="n"/>
-      <c r="Z91" s="4" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
+      <c r="W91" s="7" t="n"/>
+      <c r="X91" s="7" t="n"/>
+      <c r="Y91" s="7" t="n"/>
+      <c r="Z91" s="7" t="n"/>
     </row>
     <row r="92" ht="75" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -9638,12 +14228,12 @@
         </is>
       </c>
       <c r="T92" s="3" t="inlineStr"/>
-      <c r="U92" s="4" t="n"/>
-      <c r="V92" s="4" t="n"/>
-      <c r="W92" s="4" t="n"/>
-      <c r="X92" s="4" t="n"/>
-      <c r="Y92" s="4" t="n"/>
-      <c r="Z92" s="4" t="n"/>
+      <c r="U92" s="7" t="n"/>
+      <c r="V92" s="7" t="n"/>
+      <c r="W92" s="7" t="n"/>
+      <c r="X92" s="7" t="n"/>
+      <c r="Y92" s="7" t="n"/>
+      <c r="Z92" s="7" t="n"/>
     </row>
     <row r="93" ht="75" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -9738,12 +14328,12 @@
         </is>
       </c>
       <c r="T93" s="3" t="inlineStr"/>
-      <c r="U93" s="4" t="n"/>
-      <c r="V93" s="4" t="n"/>
-      <c r="W93" s="4" t="n"/>
-      <c r="X93" s="4" t="n"/>
-      <c r="Y93" s="4" t="n"/>
-      <c r="Z93" s="4" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
+      <c r="W93" s="7" t="n"/>
+      <c r="X93" s="7" t="n"/>
+      <c r="Y93" s="7" t="n"/>
+      <c r="Z93" s="7" t="n"/>
     </row>
     <row r="94" ht="75" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -9842,12 +14432,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U94" s="4" t="n"/>
-      <c r="V94" s="4" t="n"/>
-      <c r="W94" s="4" t="n"/>
-      <c r="X94" s="4" t="n"/>
-      <c r="Y94" s="4" t="n"/>
-      <c r="Z94" s="4" t="n"/>
+      <c r="U94" s="7" t="n"/>
+      <c r="V94" s="7" t="n"/>
+      <c r="W94" s="7" t="n"/>
+      <c r="X94" s="7" t="n"/>
+      <c r="Y94" s="7" t="n"/>
+      <c r="Z94" s="7" t="n"/>
     </row>
     <row r="95" ht="75" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -9946,12 +14536,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U95" s="4" t="n"/>
-      <c r="V95" s="4" t="n"/>
-      <c r="W95" s="4" t="n"/>
-      <c r="X95" s="4" t="n"/>
-      <c r="Y95" s="4" t="n"/>
-      <c r="Z95" s="4" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
+      <c r="W95" s="7" t="n"/>
+      <c r="X95" s="7" t="n"/>
+      <c r="Y95" s="7" t="n"/>
+      <c r="Z95" s="7" t="n"/>
     </row>
     <row r="96" ht="75" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -10050,12 +14640,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U96" s="4" t="n"/>
-      <c r="V96" s="4" t="n"/>
-      <c r="W96" s="4" t="n"/>
-      <c r="X96" s="4" t="n"/>
-      <c r="Y96" s="4" t="n"/>
-      <c r="Z96" s="4" t="n"/>
+      <c r="U96" s="7" t="n"/>
+      <c r="V96" s="7" t="n"/>
+      <c r="W96" s="7" t="n"/>
+      <c r="X96" s="7" t="n"/>
+      <c r="Y96" s="7" t="n"/>
+      <c r="Z96" s="7" t="n"/>
     </row>
     <row r="97" ht="75" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -10154,12 +14744,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U97" s="4" t="n"/>
-      <c r="V97" s="4" t="n"/>
-      <c r="W97" s="4" t="n"/>
-      <c r="X97" s="4" t="n"/>
-      <c r="Y97" s="4" t="n"/>
-      <c r="Z97" s="4" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
+      <c r="W97" s="7" t="n"/>
+      <c r="X97" s="7" t="n"/>
+      <c r="Y97" s="7" t="n"/>
+      <c r="Z97" s="7" t="n"/>
     </row>
     <row r="98" ht="75" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -10258,12 +14848,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U98" s="4" t="n"/>
-      <c r="V98" s="4" t="n"/>
-      <c r="W98" s="4" t="n"/>
-      <c r="X98" s="4" t="n"/>
-      <c r="Y98" s="4" t="n"/>
-      <c r="Z98" s="4" t="n"/>
+      <c r="U98" s="7" t="n"/>
+      <c r="V98" s="7" t="n"/>
+      <c r="W98" s="7" t="n"/>
+      <c r="X98" s="7" t="n"/>
+      <c r="Y98" s="7" t="n"/>
+      <c r="Z98" s="7" t="n"/>
     </row>
     <row r="99" ht="75" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -10362,12 +14952,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U99" s="4" t="n"/>
-      <c r="V99" s="4" t="n"/>
-      <c r="W99" s="4" t="n"/>
-      <c r="X99" s="4" t="n"/>
-      <c r="Y99" s="4" t="n"/>
-      <c r="Z99" s="4" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
+      <c r="W99" s="7" t="n"/>
+      <c r="X99" s="7" t="n"/>
+      <c r="Y99" s="7" t="n"/>
+      <c r="Z99" s="7" t="n"/>
     </row>
     <row r="100" ht="75" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -10468,12 +15058,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U100" s="4" t="n"/>
-      <c r="V100" s="4" t="n"/>
-      <c r="W100" s="4" t="n"/>
-      <c r="X100" s="4" t="n"/>
-      <c r="Y100" s="4" t="n"/>
-      <c r="Z100" s="4" t="n"/>
+      <c r="U100" s="7" t="n"/>
+      <c r="V100" s="7" t="n"/>
+      <c r="W100" s="7" t="n"/>
+      <c r="X100" s="7" t="n"/>
+      <c r="Y100" s="7" t="n"/>
+      <c r="Z100" s="7" t="n"/>
     </row>
     <row r="101" ht="75" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -10574,12 +15164,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U101" s="4" t="n"/>
-      <c r="V101" s="4" t="n"/>
-      <c r="W101" s="4" t="n"/>
-      <c r="X101" s="4" t="n"/>
-      <c r="Y101" s="4" t="n"/>
-      <c r="Z101" s="4" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
+      <c r="W101" s="7" t="n"/>
+      <c r="X101" s="7" t="n"/>
+      <c r="Y101" s="7" t="n"/>
+      <c r="Z101" s="7" t="n"/>
     </row>
     <row r="102" ht="75" customHeight="1">
       <c r="A102" s="3" t="n">
@@ -10680,12 +15270,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U102" s="4" t="n"/>
-      <c r="V102" s="4" t="n"/>
-      <c r="W102" s="4" t="n"/>
-      <c r="X102" s="4" t="n"/>
-      <c r="Y102" s="4" t="n"/>
-      <c r="Z102" s="4" t="n"/>
+      <c r="U102" s="7" t="n"/>
+      <c r="V102" s="7" t="n"/>
+      <c r="W102" s="7" t="n"/>
+      <c r="X102" s="7" t="n"/>
+      <c r="Y102" s="7" t="n"/>
+      <c r="Z102" s="7" t="n"/>
     </row>
     <row r="103" ht="75" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -10786,12 +15376,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U103" s="4" t="n"/>
-      <c r="V103" s="4" t="n"/>
-      <c r="W103" s="4" t="n"/>
-      <c r="X103" s="4" t="n"/>
-      <c r="Y103" s="4" t="n"/>
-      <c r="Z103" s="4" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
+      <c r="W103" s="7" t="n"/>
+      <c r="X103" s="7" t="n"/>
+      <c r="Y103" s="7" t="n"/>
+      <c r="Z103" s="7" t="n"/>
     </row>
     <row r="104" ht="75" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -10892,12 +15482,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U104" s="4" t="n"/>
-      <c r="V104" s="4" t="n"/>
-      <c r="W104" s="4" t="n"/>
-      <c r="X104" s="4" t="n"/>
-      <c r="Y104" s="4" t="n"/>
-      <c r="Z104" s="4" t="n"/>
+      <c r="U104" s="7" t="n"/>
+      <c r="V104" s="7" t="n"/>
+      <c r="W104" s="7" t="n"/>
+      <c r="X104" s="7" t="n"/>
+      <c r="Y104" s="7" t="n"/>
+      <c r="Z104" s="7" t="n"/>
     </row>
     <row r="105" ht="75" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -10996,12 +15586,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U105" s="4" t="n"/>
-      <c r="V105" s="4" t="n"/>
-      <c r="W105" s="4" t="n"/>
-      <c r="X105" s="4" t="n"/>
-      <c r="Y105" s="4" t="n"/>
-      <c r="Z105" s="4" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
+      <c r="W105" s="7" t="n"/>
+      <c r="X105" s="7" t="n"/>
+      <c r="Y105" s="7" t="n"/>
+      <c r="Z105" s="7" t="n"/>
     </row>
     <row r="106" ht="75" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -11100,12 +15690,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U106" s="4" t="n"/>
-      <c r="V106" s="4" t="n"/>
-      <c r="W106" s="4" t="n"/>
-      <c r="X106" s="4" t="n"/>
-      <c r="Y106" s="4" t="n"/>
-      <c r="Z106" s="4" t="n"/>
+      <c r="U106" s="7" t="n"/>
+      <c r="V106" s="7" t="n"/>
+      <c r="W106" s="7" t="n"/>
+      <c r="X106" s="7" t="n"/>
+      <c r="Y106" s="7" t="n"/>
+      <c r="Z106" s="7" t="n"/>
     </row>
     <row r="107" ht="75" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -11204,12 +15794,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U107" s="4" t="n"/>
-      <c r="V107" s="4" t="n"/>
-      <c r="W107" s="4" t="n"/>
-      <c r="X107" s="4" t="n"/>
-      <c r="Y107" s="4" t="n"/>
-      <c r="Z107" s="4" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
+      <c r="W107" s="7" t="n"/>
+      <c r="X107" s="7" t="n"/>
+      <c r="Y107" s="7" t="n"/>
+      <c r="Z107" s="7" t="n"/>
     </row>
     <row r="108" ht="75" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -11311,12 +15901,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U108" s="4" t="n"/>
-      <c r="V108" s="4" t="n"/>
-      <c r="W108" s="4" t="n"/>
-      <c r="X108" s="4" t="n"/>
-      <c r="Y108" s="4" t="n"/>
-      <c r="Z108" s="4" t="n"/>
+      <c r="U108" s="7" t="n"/>
+      <c r="V108" s="7" t="n"/>
+      <c r="W108" s="7" t="n"/>
+      <c r="X108" s="7" t="n"/>
+      <c r="Y108" s="7" t="n"/>
+      <c r="Z108" s="7" t="n"/>
     </row>
     <row r="109" ht="75" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -11418,12 +16008,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U109" s="4" t="n"/>
-      <c r="V109" s="4" t="n"/>
-      <c r="W109" s="4" t="n"/>
-      <c r="X109" s="4" t="n"/>
-      <c r="Y109" s="4" t="n"/>
-      <c r="Z109" s="4" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
+      <c r="W109" s="7" t="n"/>
+      <c r="X109" s="7" t="n"/>
+      <c r="Y109" s="7" t="n"/>
+      <c r="Z109" s="7" t="n"/>
     </row>
     <row r="110" ht="75" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -11525,12 +16115,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U110" s="4" t="n"/>
-      <c r="V110" s="4" t="n"/>
-      <c r="W110" s="4" t="n"/>
-      <c r="X110" s="4" t="n"/>
-      <c r="Y110" s="4" t="n"/>
-      <c r="Z110" s="4" t="n"/>
+      <c r="U110" s="7" t="n"/>
+      <c r="V110" s="7" t="n"/>
+      <c r="W110" s="7" t="n"/>
+      <c r="X110" s="7" t="n"/>
+      <c r="Y110" s="7" t="n"/>
+      <c r="Z110" s="7" t="n"/>
     </row>
     <row r="111" ht="75" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -11632,12 +16222,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U111" s="4" t="n"/>
-      <c r="V111" s="4" t="n"/>
-      <c r="W111" s="4" t="n"/>
-      <c r="X111" s="4" t="n"/>
-      <c r="Y111" s="4" t="n"/>
-      <c r="Z111" s="4" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
+      <c r="W111" s="7" t="n"/>
+      <c r="X111" s="7" t="n"/>
+      <c r="Y111" s="7" t="n"/>
+      <c r="Z111" s="7" t="n"/>
     </row>
     <row r="112" ht="75" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -11739,12 +16329,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U112" s="4" t="n"/>
-      <c r="V112" s="4" t="n"/>
-      <c r="W112" s="4" t="n"/>
-      <c r="X112" s="4" t="n"/>
-      <c r="Y112" s="4" t="n"/>
-      <c r="Z112" s="4" t="n"/>
+      <c r="U112" s="7" t="n"/>
+      <c r="V112" s="7" t="n"/>
+      <c r="W112" s="7" t="n"/>
+      <c r="X112" s="7" t="n"/>
+      <c r="Y112" s="7" t="n"/>
+      <c r="Z112" s="7" t="n"/>
     </row>
     <row r="113" ht="75" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -11846,12 +16436,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U113" s="4" t="n"/>
-      <c r="V113" s="4" t="n"/>
-      <c r="W113" s="4" t="n"/>
-      <c r="X113" s="4" t="n"/>
-      <c r="Y113" s="4" t="n"/>
-      <c r="Z113" s="4" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
+      <c r="W113" s="7" t="n"/>
+      <c r="X113" s="7" t="n"/>
+      <c r="Y113" s="7" t="n"/>
+      <c r="Z113" s="7" t="n"/>
     </row>
     <row r="114" ht="75" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -11957,12 +16547,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U114" s="4" t="n"/>
-      <c r="V114" s="4" t="n"/>
-      <c r="W114" s="4" t="n"/>
-      <c r="X114" s="4" t="n"/>
-      <c r="Y114" s="4" t="n"/>
-      <c r="Z114" s="4" t="n"/>
+      <c r="U114" s="7" t="n"/>
+      <c r="V114" s="7" t="n"/>
+      <c r="W114" s="7" t="n"/>
+      <c r="X114" s="7" t="n"/>
+      <c r="Y114" s="7" t="n"/>
+      <c r="Z114" s="7" t="n"/>
     </row>
     <row r="115" ht="75" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -12068,12 +16658,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U115" s="4" t="n"/>
-      <c r="V115" s="4" t="n"/>
-      <c r="W115" s="4" t="n"/>
-      <c r="X115" s="4" t="n"/>
-      <c r="Y115" s="4" t="n"/>
-      <c r="Z115" s="4" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
+      <c r="W115" s="7" t="n"/>
+      <c r="X115" s="7" t="n"/>
+      <c r="Y115" s="7" t="n"/>
+      <c r="Z115" s="7" t="n"/>
     </row>
     <row r="116" ht="75" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -12179,12 +16769,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U116" s="4" t="n"/>
-      <c r="V116" s="4" t="n"/>
-      <c r="W116" s="4" t="n"/>
-      <c r="X116" s="4" t="n"/>
-      <c r="Y116" s="4" t="n"/>
-      <c r="Z116" s="4" t="n"/>
+      <c r="U116" s="7" t="n"/>
+      <c r="V116" s="7" t="n"/>
+      <c r="W116" s="7" t="n"/>
+      <c r="X116" s="7" t="n"/>
+      <c r="Y116" s="7" t="n"/>
+      <c r="Z116" s="7" t="n"/>
     </row>
     <row r="117" ht="75" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -12290,12 +16880,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U117" s="4" t="n"/>
-      <c r="V117" s="4" t="n"/>
-      <c r="W117" s="4" t="n"/>
-      <c r="X117" s="4" t="n"/>
-      <c r="Y117" s="4" t="n"/>
-      <c r="Z117" s="4" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
+      <c r="W117" s="7" t="n"/>
+      <c r="X117" s="7" t="n"/>
+      <c r="Y117" s="7" t="n"/>
+      <c r="Z117" s="7" t="n"/>
     </row>
     <row r="118" ht="75" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -12393,12 +16983,12 @@
       </c>
       <c r="S118" s="3" t="inlineStr"/>
       <c r="T118" s="3" t="inlineStr"/>
-      <c r="U118" s="4" t="n"/>
-      <c r="V118" s="4" t="n"/>
-      <c r="W118" s="4" t="n"/>
-      <c r="X118" s="4" t="n"/>
-      <c r="Y118" s="4" t="n"/>
-      <c r="Z118" s="4" t="n"/>
+      <c r="U118" s="7" t="n"/>
+      <c r="V118" s="7" t="n"/>
+      <c r="W118" s="7" t="n"/>
+      <c r="X118" s="7" t="n"/>
+      <c r="Y118" s="7" t="n"/>
+      <c r="Z118" s="7" t="n"/>
     </row>
     <row r="119" ht="75" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -12489,12 +17079,12 @@
       </c>
       <c r="S119" s="3" t="inlineStr"/>
       <c r="T119" s="3" t="inlineStr"/>
-      <c r="U119" s="4" t="n"/>
-      <c r="V119" s="4" t="n"/>
-      <c r="W119" s="4" t="n"/>
-      <c r="X119" s="4" t="n"/>
-      <c r="Y119" s="4" t="n"/>
-      <c r="Z119" s="4" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
+      <c r="W119" s="7" t="n"/>
+      <c r="X119" s="7" t="n"/>
+      <c r="Y119" s="7" t="n"/>
+      <c r="Z119" s="7" t="n"/>
     </row>
     <row r="120" ht="75" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -12588,12 +17178,12 @@
       </c>
       <c r="S120" s="3" t="inlineStr"/>
       <c r="T120" s="3" t="inlineStr"/>
-      <c r="U120" s="4" t="n"/>
-      <c r="V120" s="4" t="n"/>
-      <c r="W120" s="4" t="n"/>
-      <c r="X120" s="4" t="n"/>
-      <c r="Y120" s="4" t="n"/>
-      <c r="Z120" s="4" t="n"/>
+      <c r="U120" s="7" t="n"/>
+      <c r="V120" s="7" t="n"/>
+      <c r="W120" s="7" t="n"/>
+      <c r="X120" s="7" t="n"/>
+      <c r="Y120" s="7" t="n"/>
+      <c r="Z120" s="7" t="n"/>
     </row>
     <row r="121" ht="75" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -12687,12 +17277,12 @@
       </c>
       <c r="S121" s="3" t="inlineStr"/>
       <c r="T121" s="3" t="inlineStr"/>
-      <c r="U121" s="4" t="n"/>
-      <c r="V121" s="4" t="n"/>
-      <c r="W121" s="4" t="n"/>
-      <c r="X121" s="4" t="n"/>
-      <c r="Y121" s="4" t="n"/>
-      <c r="Z121" s="4" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
+      <c r="W121" s="7" t="n"/>
+      <c r="X121" s="7" t="n"/>
+      <c r="Y121" s="7" t="n"/>
+      <c r="Z121" s="7" t="n"/>
     </row>
     <row r="122" ht="75" customHeight="1">
       <c r="A122" s="3" t="n">
@@ -12786,12 +17376,12 @@
       </c>
       <c r="S122" s="3" t="inlineStr"/>
       <c r="T122" s="3" t="inlineStr"/>
-      <c r="U122" s="4" t="n"/>
-      <c r="V122" s="4" t="n"/>
-      <c r="W122" s="4" t="n"/>
-      <c r="X122" s="4" t="n"/>
-      <c r="Y122" s="4" t="n"/>
-      <c r="Z122" s="4" t="n"/>
+      <c r="U122" s="7" t="n"/>
+      <c r="V122" s="7" t="n"/>
+      <c r="W122" s="7" t="n"/>
+      <c r="X122" s="7" t="n"/>
+      <c r="Y122" s="7" t="n"/>
+      <c r="Z122" s="7" t="n"/>
     </row>
     <row r="123" ht="75" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -12885,12 +17475,12 @@
       </c>
       <c r="S123" s="3" t="inlineStr"/>
       <c r="T123" s="3" t="inlineStr"/>
-      <c r="U123" s="4" t="n"/>
-      <c r="V123" s="4" t="n"/>
-      <c r="W123" s="4" t="n"/>
-      <c r="X123" s="4" t="n"/>
-      <c r="Y123" s="4" t="n"/>
-      <c r="Z123" s="4" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
+      <c r="W123" s="7" t="n"/>
+      <c r="X123" s="7" t="n"/>
+      <c r="Y123" s="7" t="n"/>
+      <c r="Z123" s="7" t="n"/>
     </row>
     <row r="124" ht="75" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -12984,12 +17574,12 @@
       </c>
       <c r="S124" s="3" t="inlineStr"/>
       <c r="T124" s="3" t="inlineStr"/>
-      <c r="U124" s="4" t="n"/>
-      <c r="V124" s="4" t="n"/>
-      <c r="W124" s="4" t="n"/>
-      <c r="X124" s="4" t="n"/>
-      <c r="Y124" s="4" t="n"/>
-      <c r="Z124" s="4" t="n"/>
+      <c r="U124" s="7" t="n"/>
+      <c r="V124" s="7" t="n"/>
+      <c r="W124" s="7" t="n"/>
+      <c r="X124" s="7" t="n"/>
+      <c r="Y124" s="7" t="n"/>
+      <c r="Z124" s="7" t="n"/>
     </row>
     <row r="125" ht="75" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -13083,12 +17673,12 @@
       </c>
       <c r="S125" s="3" t="inlineStr"/>
       <c r="T125" s="3" t="inlineStr"/>
-      <c r="U125" s="4" t="n"/>
-      <c r="V125" s="4" t="n"/>
-      <c r="W125" s="4" t="n"/>
-      <c r="X125" s="4" t="n"/>
-      <c r="Y125" s="4" t="n"/>
-      <c r="Z125" s="4" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
+      <c r="W125" s="7" t="n"/>
+      <c r="X125" s="7" t="n"/>
+      <c r="Y125" s="7" t="n"/>
+      <c r="Z125" s="7" t="n"/>
     </row>
     <row r="126" ht="75" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -13187,12 +17777,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U126" s="4" t="n"/>
-      <c r="V126" s="4" t="n"/>
-      <c r="W126" s="4" t="n"/>
-      <c r="X126" s="4" t="n"/>
-      <c r="Y126" s="4" t="n"/>
-      <c r="Z126" s="4" t="n"/>
+      <c r="U126" s="7" t="n"/>
+      <c r="V126" s="7" t="n"/>
+      <c r="W126" s="7" t="n"/>
+      <c r="X126" s="7" t="n"/>
+      <c r="Y126" s="7" t="n"/>
+      <c r="Z126" s="7" t="n"/>
     </row>
     <row r="127" ht="75" customHeight="1">
       <c r="A127" s="3" t="n">
@@ -13291,12 +17881,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U127" s="4" t="n"/>
-      <c r="V127" s="4" t="n"/>
-      <c r="W127" s="4" t="n"/>
-      <c r="X127" s="4" t="n"/>
-      <c r="Y127" s="4" t="n"/>
-      <c r="Z127" s="4" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
+      <c r="W127" s="7" t="n"/>
+      <c r="X127" s="7" t="n"/>
+      <c r="Y127" s="7" t="n"/>
+      <c r="Z127" s="7" t="n"/>
     </row>
     <row r="128" ht="75" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -13395,12 +17985,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U128" s="4" t="n"/>
-      <c r="V128" s="4" t="n"/>
-      <c r="W128" s="4" t="n"/>
-      <c r="X128" s="4" t="n"/>
-      <c r="Y128" s="4" t="n"/>
-      <c r="Z128" s="4" t="n"/>
+      <c r="U128" s="7" t="n"/>
+      <c r="V128" s="7" t="n"/>
+      <c r="W128" s="7" t="n"/>
+      <c r="X128" s="7" t="n"/>
+      <c r="Y128" s="7" t="n"/>
+      <c r="Z128" s="7" t="n"/>
     </row>
     <row r="129" ht="75" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -13491,12 +18081,12 @@
       </c>
       <c r="S129" s="3" t="inlineStr"/>
       <c r="T129" s="3" t="inlineStr"/>
-      <c r="U129" s="4" t="n"/>
-      <c r="V129" s="4" t="n"/>
-      <c r="W129" s="4" t="n"/>
-      <c r="X129" s="4" t="n"/>
-      <c r="Y129" s="4" t="n"/>
-      <c r="Z129" s="4" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
+      <c r="W129" s="7" t="n"/>
+      <c r="X129" s="7" t="n"/>
+      <c r="Y129" s="7" t="n"/>
+      <c r="Z129" s="7" t="n"/>
     </row>
     <row r="130" ht="75" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -13587,12 +18177,12 @@
       </c>
       <c r="S130" s="3" t="inlineStr"/>
       <c r="T130" s="3" t="inlineStr"/>
-      <c r="U130" s="4" t="n"/>
-      <c r="V130" s="4" t="n"/>
-      <c r="W130" s="4" t="n"/>
-      <c r="X130" s="4" t="n"/>
-      <c r="Y130" s="4" t="n"/>
-      <c r="Z130" s="4" t="n"/>
+      <c r="U130" s="7" t="n"/>
+      <c r="V130" s="7" t="n"/>
+      <c r="W130" s="7" t="n"/>
+      <c r="X130" s="7" t="n"/>
+      <c r="Y130" s="7" t="n"/>
+      <c r="Z130" s="7" t="n"/>
     </row>
     <row r="131" ht="75" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -13683,12 +18273,12 @@
       </c>
       <c r="S131" s="3" t="inlineStr"/>
       <c r="T131" s="3" t="inlineStr"/>
-      <c r="U131" s="4" t="n"/>
-      <c r="V131" s="4" t="n"/>
-      <c r="W131" s="4" t="n"/>
-      <c r="X131" s="4" t="n"/>
-      <c r="Y131" s="4" t="n"/>
-      <c r="Z131" s="4" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
+      <c r="W131" s="7" t="n"/>
+      <c r="X131" s="7" t="n"/>
+      <c r="Y131" s="7" t="n"/>
+      <c r="Z131" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13696,7 +18286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13972,12 +18562,12 @@
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
+      <c r="W4" s="7" t="n"/>
+      <c r="X4" s="7" t="n"/>
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -14078,12 +18668,12 @@
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
+      <c r="W5" s="7" t="n"/>
+      <c r="X5" s="7" t="n"/>
+      <c r="Y5" s="7" t="n"/>
+      <c r="Z5" s="7" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -14174,12 +18764,12 @@
           <t>каталожный номер 065B7474</t>
         </is>
       </c>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="7" t="n"/>
+      <c r="W6" s="7" t="n"/>
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="7" t="n"/>
+      <c r="Z6" s="7" t="n"/>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -14270,12 +18860,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
+      <c r="W7" s="7" t="n"/>
+      <c r="X7" s="7" t="n"/>
+      <c r="Y7" s="7" t="n"/>
+      <c r="Z7" s="7" t="n"/>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -14362,12 +18952,12 @@
           <t>Каталожный № 082X8477R</t>
         </is>
       </c>
-      <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -14459,12 +19049,12 @@
           <t>Затвор фланцевый 32нж910р Ду1000 Ру10 с эл.приводом с комплектом ответных фланцев (90 гр. указатель поворота- визуальны и встроенный дистанционный блок (токовый выход) указателя положения (открыто, закрыто)</t>
         </is>
       </c>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -14543,12 +19133,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -14627,12 +19217,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
+      <c r="Z11" s="7" t="n"/>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -14711,12 +19301,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -14815,12 +19405,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -14903,12 +19493,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
     </row>
     <row r="15" ht="75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -14991,12 +19581,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
     </row>
     <row r="16" ht="75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -15079,12 +19669,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
     </row>
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -15167,12 +19757,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M38936</t>
         </is>
       </c>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
     </row>
     <row r="18" ht="75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -15271,12 +19861,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -15375,12 +19965,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
     </row>
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -15479,12 +20069,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -15579,12 +20169,12 @@
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n"/>
+      <c r="Y21" s="7" t="n"/>
+      <c r="Z21" s="7" t="n"/>
     </row>
     <row r="22" ht="75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -15675,12 +20265,12 @@
       </c>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n"/>
-      <c r="W22" s="4" t="n"/>
-      <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="4" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
+      <c r="W22" s="7" t="n"/>
+      <c r="X22" s="7" t="n"/>
+      <c r="Y22" s="7" t="n"/>
+      <c r="Z22" s="7" t="n"/>
     </row>
     <row r="23" ht="75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -15771,12 +20361,12 @@
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="4" t="n"/>
-      <c r="V23" s="4" t="n"/>
-      <c r="W23" s="4" t="n"/>
-      <c r="X23" s="4" t="n"/>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="4" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
+      <c r="W23" s="7" t="n"/>
+      <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="7" t="n"/>
+      <c r="Z23" s="7" t="n"/>
     </row>
     <row r="24" ht="75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -15875,12 +20465,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U24" s="4" t="n"/>
-      <c r="V24" s="4" t="n"/>
-      <c r="W24" s="4" t="n"/>
-      <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="4" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="7" t="n"/>
+      <c r="X24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n"/>
+      <c r="Z24" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15888,7 +20478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16120,12 +20710,12 @@
           <t>Рыбозащитное устройство с потокообразователем РОП-200, под производительность насоса от 250 куб м/час. В комплекте переход на трубу ДУ 200 Материал изготовления ст.20. Покраска РОП — серебрянка. Диаметр заградительной ячейки — 4мм (длина защищаемой молоди рыбы длиной от 30мм)</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
+      <c r="W4" s="7" t="n"/>
+      <c r="X4" s="7" t="n"/>
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -16176,12 +20766,12 @@
           <t>Степень защиты IP 54, Питающее напряжение 230 V AC, Схема включения Z20, Выключающая сила 2 900 N, Макс. нагрузочная сила 2 500 N, Скорость управления 4 mm/min,  Электродвигатель 1 W, Выключение злектропривода от нагрузки Двухсиловое (Схема включения Z20 выключатели S1, S2), Рабочий ход с датчиком 25 mm, Датчик положения Электронный с R/I преобразователем с токовым сигналом С источником, Включение 2-проводник, Выход 4 - 20 mA, Схема включения Z269, Механическое присоединение Столбикы, Присоединительная высота 110мм, Прицоедин. резьба тяги M8x1-22, Эскиз P-1185/B, 2 добавочные выключатели положения, Схема включения Z21.</t>
         </is>
       </c>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
+      <c r="W5" s="7" t="n"/>
+      <c r="X5" s="7" t="n"/>
+      <c r="Y5" s="7" t="n"/>
+      <c r="Z5" s="7" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -16276,12 +20866,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="7" t="n"/>
+      <c r="W6" s="7" t="n"/>
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="7" t="n"/>
+      <c r="Z6" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
+++ b/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
@@ -491,14 +491,14 @@
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
@@ -584,7 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="105" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>124 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="105" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
@@ -657,7 +657,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>96 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="105" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
@@ -714,7 +714,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>89 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="105" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
@@ -771,7 +771,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>101 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="105" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>5</v>
       </c>
@@ -828,7 +828,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>117 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="105" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>96 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="105" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
@@ -942,7 +942,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
+          <t>4 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -983,7 +983,7 @@
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
@@ -999,7 +999,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91, 1.3/32, 1.3/33, 1.3/34</t>
+          <t>15 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1040,7 +1040,7 @@
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1.3/154, 1.3/155, 1.3/156, 1.3/158, 1.3/159, 1.3/161, 1.6/89, 1.6/90, 1.6/91</t>
+          <t>9 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1097,7 +1097,7 @@
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="105" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91, 1.1/22, 1.1/23</t>
+          <t>14 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="105" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>11</v>
       </c>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1.1/23, 1.1/22, 1.3/150, 1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91</t>
+          <t>15 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1211,7 +1211,7 @@
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="105" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>12</v>
       </c>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1.3/150, 1.1/23, 1.1/22</t>
+          <t>3 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="105" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>13</v>
       </c>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1.3/151, 1.3/152, 1.3/153</t>
+          <t>3 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>14</v>
       </c>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1.3/151, 1.3/152, 1.3/153</t>
+          <t>3 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1382,7 +1382,7 @@
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="105" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>15</v>
       </c>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>1.3/163, 1.6/93</t>
+          <t>2 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="105" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>16</v>
       </c>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1.3/163</t>
+          <t>1 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1496,7 +1496,7 @@
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="105" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>17</v>
       </c>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="105" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>18</v>
       </c>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">

--- a/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
+++ b/KAMCHATKA_REMAINING_ZAVODY_SPEC.xlsx
@@ -40,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,9 +107,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -989,52 +981,52 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ООО «Торговый Дом АДЛ» (бренды «Гранвэл», «Гранлок»)</t>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Московская обл. (производственный комплекс, 4 цеха, &gt;31 000 м²; адрес площадки на сайте не указан; склад — Лыткарино; «Ступино» на сайте НЕ подтверждено)</t>
+          <t>Рыбинск (Ярославская обл.)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>15 поз. — список на листе «Покрытие»</t>
+          <t>1 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Оригинал позиций ТЗ: ЗПВС-FL(W)-3-…-MN-E/MR-E (= «FL(w)-3-MR-E», «ЗПВС») DN65/80/100/150/200 PN16 и ЗПТЛ-FLN(W)-5-…-HT (= «ЗП ТЛ», седло EPDM HT, до +130 °C) DN80/100/150/200 PN16 — все 12 чугунных ме</t>
+          <t>Кран шаровый муфтовый Ду6–50, Ру до 6,3 МПа; корпус 1.4408 (литьё, аналог CF8M/AISI 316 ≈ 08Х17Н13М2) или 12Х18Н9ТЛ/12Х18Н10Т; седло фторопласт Ф4; серии МОНО/ЭКОНОМ/РЕТРО. ВНИМАНИЕ: на сайте температ</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>На сайте: «дисковые поворотные затворы «Гранвэл»» — в числе продукции с заключением Минпромторга по ПП 719 (новость 11.0</t>
+          <t>не найдено (запросить у завода)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Владивосток +7 (984) 159-21-64</t>
+          <t>8-800-700-62-60; отдел продаж +7 (4855) 21-77-88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>info@adl.ru; granvel@adl.ru</t>
+          <t>info@fobosarm.ru</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://adl.ru</t>
+          <t>fobosarm.ru</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68 и info@adl.ru — в шапке каждой страницы и на странице «Контакты» (центральный офис: Москва, пр-т Андропова, 18, корп. 7); granvel@adl.ru — на</t>
+          <t>8-800-700-62-60 и info@fobosarm.ru совпадают на главной, стр. «О компании», карточке крана и стр. «Контакты» (проверено 23.10.2026)</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://adl.ru/truboprovodnaya-armatura/zatvory-diskovye-povorotnye/filter/brend-granvel/</t>
+          <t>https://fobosarm.ru/products/kran-sharovyy-muftovyy/</t>
         </is>
       </c>
       <c r="L11" s="3" t="n"/>
@@ -1046,52 +1038,52 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ОАО «Литейно-механический завод» (ОАО «ЛМЗ»)</t>
+          <t>ООО «Торговый Дом АДЛ» (бренды «Гранвэл», «Гранлок»)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Нижегородская обл., г. Семёнов, ул. Промышленная, 3</t>
+          <t>Московская обл. (производственный комплекс, 4 цеха, &gt;31 000 м²; адрес площадки на сайте не указан; склад — Лыткарино; «Ступино» на сайте НЕ подтверждено)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>9 поз. — список на листе «Покрытие»</t>
+          <t>15 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Затвор 32ч1р межфланцевый с рукояткой, корпус/диск СЧ20 (DN50–150), манжета EPDM, класс А, PN16 для DN50–150, до +115 °C. DN200 — только PN10 (ВЧ50) → 1.3/157 и 1.3/160 (Ду200 Ру16) НЕ закрывает; DN65</t>
+          <t>Оригинал позиций ТЗ: ЗПВС-FL(W)-3-…-MN-E/MR-E (= «FL(w)-3-MR-E», «ЗПВС») DN65/80/100/150/200 PN16 и ЗПТЛ-FLN(W)-5-…-HT (= «ЗП ТЛ», седло EPDM HT, до +130 °C) DN80/100/150/200 PN16 — все 12 чугунных ме</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>На сайте: «продукция нашего завода внесена в реестр Минпромторга» (новость 16.05.2025, https://www.semlmz.ru/novosti), п</t>
+          <t>На сайте: «дисковые поворотные затворы «Гранвэл»» — в числе продукции с заключением Минпромторга по ПП 719 (новость 11.0</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>+7 (83162) 5-70-90</t>
+          <t>+7 (495) 937-89-68; Владивосток +7 (984) 159-21-64</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>marketlmz@mail.ru</t>
+          <t>info@adl.ru; granvel@adl.ru</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://www.semlmz.ru</t>
+          <t>https://adl.ru</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (83162) 5-70-90 — в шапке, подвале и на странице «Контакты»; marketlmz@mail.ru — в шапке всех страниц и mailto на главной (на «Контактах» адреса руководства </t>
+          <t>+7 (495) 937-89-68 и info@adl.ru — в шапке каждой страницы и на странице «Контакты» (центральный офис: Москва, пр-т Андропова, 18, корп. 7); granvel@adl.ru — на</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.semlmz.ru/zatvor-32ch1r</t>
+          <t>https://adl.ru/truboprovodnaya-armatura/zatvory-diskovye-povorotnye/filter/brend-granvel/</t>
         </is>
       </c>
       <c r="L12" s="3" t="n"/>
@@ -1103,52 +1095,52 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
+          <t>ОАО «Литейно-механический завод» (ОАО «ЛМЗ»)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
+          <t>Нижегородская обл., г. Семёнов, ул. Промышленная, 3</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>14 поз. — список на листе «Покрытие»</t>
+          <t>9 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
+          <t>Затвор 32ч1р межфланцевый с рукояткой, корпус/диск СЧ20 (DN50–150), манжета EPDM, класс А, PN16 для DN50–150, до +115 °C. DN200 — только PN10 (ВЧ50) → 1.3/157 и 1.3/160 (Ду200 Ру16) НЕ закрывает; DN65</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
+          <t>На сайте: «продукция нашего завода внесена в реестр Минпромторга» (новость 16.05.2025, https://www.semlmz.ru/novosti), п</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (83162) 5-70-90</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>info@aoutk.ru</t>
+          <t>marketlmz@mail.ru</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://aoutk.ru</t>
+          <t>https://www.semlmz.ru</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>+73513077109 и info@aoutk.ru — в шапке всех страниц и на странице «Контакты» (факт. адрес Озёрск, Индустриальная, 4). Совпадает.</t>
+          <t xml:space="preserve">+7 (83162) 5-70-90 — в шапке, подвале и на странице «Контакты»; marketlmz@mail.ru — в шапке всех страниц и mailto на главной (на «Контактах» адреса руководства </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://aoutk.ru/catalog/butterfly-valves/elastomeric-seat/</t>
+          <t>https://www.semlmz.ru/zatvor-32ch1r</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -1160,52 +1152,52 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» (PromArm®)</t>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
+          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>15 поз. — список на листе «Покрытие»</t>
+          <t>14 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
+          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гигиенический; упоминаний реестра ПП 719 не</t>
+          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (351) 307-71-09</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>info@promarm.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
+          <t>https://aoutk.ru</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97 и +7 (495) 668-10-92 — в подвале каждой страницы и на «Контактах» (7 вхождений); info@promarm.ru — в шапке и на «Контактах» (12 вхождений). В</t>
+          <t>+73513077109 и info@aoutk.ru — в шапке всех страниц и на странице «Контакты» (факт. адрес Озёрск, Индустриальная, 4). Совпадает.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.promarm.com/catalog/pipeline_valves/butterfly_valves/pa_900/zatvor_pa_954_450_10_05_dn_450_pn_10/</t>
+          <t>https://aoutk.ru/catalog/butterfly-valves/elastomeric-seat/</t>
         </is>
       </c>
       <c r="L14" s="3" t="n"/>
@@ -1217,52 +1209,52 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
+          <t>ООО «ПромАрм» (PromArm®)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>г. Пенза (промкомплекс 225 000 м²)</t>
+          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3 поз. — список на листе «Покрытие»</t>
+          <t>15 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
+          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гигиенический; упоминаний реестра ПП 719 не</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (продажи)</t>
+          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>sales@ptpa.ru</t>
+          <t>info@promarm.ru</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://ptpa.ru</t>
+          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 и sales@ptpa.ru — в шапке всех страниц и на «Контактах» (отдел продаж). Совпадает.</t>
+          <t>+7 (8412) 35-07-97 и +7 (495) 668-10-92 — в подвале каждой страницы и на «Контактах» (7 вхождений); info@promarm.ru — в шапке и на «Контактах» (12 вхождений). В</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://ptpa.ru/catalog/zatvory-diskovye/zatvory-diskovye-povorotnye-stalnye/</t>
+          <t>https://www.promarm.com/catalog/pipeline_valves/butterfly_valves/pa_900/zatvor_pa_954_450_10_05_dn_450_pn_10/</t>
         </is>
       </c>
       <c r="L15" s="3" t="n"/>
@@ -1274,12 +1266,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ООО «ЭнергоПромАтомСервис» (ООО «ЭПАС»)</t>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>г. Екатеринбург, ул. Электриков, 18Б</t>
+          <t>г. Пенза (промкомплекс 225 000 м²)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1289,37 +1281,37 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Точная маркировка ТЗ: «ЗДП-150-6,3-1-М-А-УХЛ1» (конфигуратор на карточке), ЗДП-50/80/100/125/150/200, PN 0,63 МПа, корпус и диск — алюминий АК12оч, класс А, рукоятка, для трансформаторного масла. «Зат</t>
+          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено на сайте</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>+7 (343) 211-02-63 (комплектующие для трансформаторов)</t>
+          <t>8 800 444-00-28 (продажи)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>epas-z@mail.ru</t>
+          <t>sales@ptpa.ru</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://epasworld.com</t>
+          <t>https://ptpa.ru</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>+7 (343) 211-02-63 и epas-z@mail.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
+          <t>8 800 444-00-28 и sales@ptpa.ru — в шапке всех страниц и на «Контактах» (отдел продаж). Совпадает.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://epasworld.com/product/%D0%B7%D0%B4%D0%BF150/</t>
+          <t>https://ptpa.ru/catalog/zatvory-diskovye/zatvory-diskovye-povorotnye-stalnye/</t>
         </is>
       </c>
       <c r="L16" s="3" t="n"/>
@@ -1331,12 +1323,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ООО «Транс-Энерго» / ООО «Лидер-Энерго» (одна группа, сайт lider-energo.ru)</t>
+          <t>ООО «ЭнергоПромАтомСервис» (ООО «ЭПАС»)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>г. Тольятти, ул. 40 лет Победы, 14 (литейный, механический, сборочный цеха — «производится нашей производственной компанией ООО Транс-Энерго»)</t>
+          <t>г. Екатеринбург, ул. Электриков, 18Б</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1346,37 +1338,37 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Держатель ТУ из ТЗ: каталог ЗПД — «затворы поворотные дисковые … изготавливаемые по ТУ 28.14.13-012-09338969-2019», ЗПД-50/80/100/125/150/200, Pном 0,63 МПа, трансформаторное масло, УХЛ1, класс А, руч</t>
+          <t>Точная маркировка ТЗ: «ЗДП-150-6,3-1-М-А-УХЛ1» (конфигуратор на карточке), ЗДП-50/80/100/125/150/200, PN 0,63 МПа, корпус и диск — алюминий АК12оч, класс А, рукоятка, для трансформаторного масла. «Зат</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>не найдено (поиск по сайту «реестр» — 0 результатов)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>+7 (8482) 21-66-32</t>
+          <t>+7 (343) 211-02-63 (комплектующие для трансформаторов)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>trans-energo@bk.ru</t>
+          <t>epas-z@mail.ru</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://lider-energo.ru</t>
+          <t>https://epasworld.com</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>+7 (8482) 21-66-32 и trans-energo@bk.ru — в шапке всех страниц и на «Контактах» (там же info@lider-energo.ru). Совпадает.</t>
+          <t>+7 (343) 211-02-63 и epas-z@mail.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://lider-energo.ru/product/zatvory-diskovye-povorotnye-du-150-transformatornye</t>
+          <t>https://epasworld.com/product/%D0%B7%D0%B4%D0%BF150/</t>
         </is>
       </c>
       <c r="L17" s="3" t="n"/>
@@ -1388,52 +1380,52 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+          <t>ООО «Транс-Энерго» / ООО «Лидер-Энерго» (одна группа, сайт lider-energo.ru)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
+          <t>г. Тольятти, ул. 40 лет Победы, 14 (литейный, механический, сборочный цеха — «производится нашей производственной компанией ООО Транс-Энерго»)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2 поз. — список на листе «Покрытие»</t>
+          <t>3 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
+          <t>Держатель ТУ из ТЗ: каталог ЗПД — «затворы поворотные дисковые … изготавливаемые по ТУ 28.14.13-012-09338969-2019», ЗПД-50/80/100/125/150/200, Pном 0,63 МПа, трансформаторное масло, УХЛ1, класс А, руч</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>не найдено (поиск по сайту «реестр» — 0 результатов)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>+7 (8352) 30-51-48</t>
+          <t>+7 (8482) 21-66-32</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>sales@zeim.ru</t>
+          <t>trans-energo@bk.ru</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru</t>
+          <t>https://lider-energo.ru</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>+7 (8352) 30-51-48 (= «(8352) 305-148» в подвале) и sales@zeim.ru — на «Контактах» и в подвале всех страниц. Совпадает.</t>
+          <t>+7 (8482) 21-66-32 и trans-energo@bk.ru — в шапке всех страниц и на «Контактах» (там же info@lider-energo.ru). Совпадает.</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru/production/mep/</t>
+          <t>https://lider-energo.ru/product/zatvory-diskovye-povorotnye-du-150-transformatornye</t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -1445,52 +1437,52 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
+          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1 поз. — список на листе «Покрытие»</t>
+          <t>2 поз. — список на листе «Покрытие»</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
+          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено на сайте</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>8 (843) 558-25-28</t>
+          <t>+7 (8352) 30-51-48</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>info@promav.ru</t>
+          <t>sales@zeim.ru</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://www.promav.ru</t>
+          <t>https://www.zeim.ru</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>8(843)558-25-28 и info@promav.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
+          <t>+7 (8352) 30-51-48 (= «(8352) 305-148» в подвале) и sales@zeim.ru — на «Контактах» и в подвале всех страниц. Совпадает.</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.promav.ru/catalog/ustrojstva-avtomatizatsii/mep/</t>
+          <t>https://www.zeim.ru/production/mep/</t>
         </is>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -1502,12 +1494,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПКФ «ТЕРМ»</t>
+          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>г. Саратов, ул. Танкистов, 195</t>
+          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1517,7 +1509,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
+          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1527,27 +1519,27 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>+7 (927) 279-09-83</t>
+          <t>8 (843) 558-25-28</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>term1998@yandex.ru</t>
+          <t>info@promav.ru</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru</t>
+          <t>https://www.promav.ru</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>+7 (927) 279-09-83 — в шапке и в блоке «Контактная информация»; term1998@yandex.ru — mailto и в блоке контактов. Одностраничный сайт — два места на одной страни</t>
+          <t>8(843)558-25-28 и info@promav.ru — в шапке всех страниц и на «Контактах». Совпадает.</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru/#harakteristiki</t>
+          <t>https://www.promav.ru/catalog/ustrojstva-avtomatizatsii/mep/</t>
         </is>
       </c>
       <c r="L20" s="3" t="n"/>
@@ -1559,12 +1551,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ООО «Регул»</t>
+          <t>ООО «ПКФ «ТЕРМ»</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
+          <t>г. Саратов, ул. Танкистов, 195</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1574,7 +1566,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
+          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1584,31 +1576,88 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (927) 279-09-83</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>regyl21@mail.ru</t>
+          <t>term1998@yandex.ru</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://regul21.ru</t>
+          <t>https://pkfterm.ru</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06 и regyl21@mail.ru — в шапке, подвале и на «Контактах». Совпадает.</t>
+          <t>+7 (927) 279-09-83 — в шапке и в блоке «Контактная информация»; term1998@yandex.ru — mailto и в блоке контактов. Одностраничный сайт — два места на одной страни</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://regul21.ru/products/rybozashchitnye-ustrojstva</t>
+          <t>https://pkfterm.ru/#harakteristiki</t>
         </is>
       </c>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="105" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Регул»</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1 поз. — список на листе «Покрытие»</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>+7 (499) 653-65-06</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>regyl21@mail.ru</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://regul21.ru</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>+7 (499) 653-65-06 и regyl21@mail.ru — в шапке, подвале и на «Контактах». Совпадает.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://regul21.ru/products/rybozashchitnye-ustrojstva</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2271,12 +2320,12 @@
       <c r="C28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
+      <c r="D28" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — не закрыта: у проверенных заводов нет нерж. муфтового Ду15 на Ру63 — искать дополнительно</t>
+          <t>ЗАО «Арматурная Компания «ФОБОС» — Фобос: на сайте до +160 °С (в ТЗ до +180 °С) и корпус 1.4408 вместо 08Х17Н13М2 — подтвердить у завода письменно</t>
         </is>
       </c>
     </row>
@@ -5437,12 +5486,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="n"/>
-      <c r="Y4" s="7" t="n"/>
-      <c r="Z4" s="7" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -5537,12 +5586,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -5633,12 +5682,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
+      <c r="Z6" s="6" t="n"/>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -5733,12 +5782,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
-      <c r="Z7" s="7" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -5829,12 +5878,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -5929,12 +5978,12 @@
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
+      <c r="Z9" s="6" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -6029,12 +6078,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
+      <c r="Z10" s="6" t="n"/>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -6129,12 +6178,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -6225,12 +6274,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
-      <c r="Z12" s="7" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -6325,12 +6374,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
+      <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -6425,12 +6474,12 @@
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
     </row>
     <row r="15" ht="75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -6525,12 +6574,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
     </row>
     <row r="16" ht="75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -6629,12 +6678,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
     </row>
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -6725,12 +6774,12 @@
       </c>
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="7" t="n"/>
-      <c r="Z17" s="7" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
     </row>
     <row r="18" ht="75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -6825,12 +6874,12 @@
           <t>(класс гермитичности "А" по ГОСТ 9544-2015).</t>
         </is>
       </c>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="n"/>
-      <c r="X18" s="7" t="n"/>
-      <c r="Y18" s="7" t="n"/>
-      <c r="Z18" s="7" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -6925,12 +6974,12 @@
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="7" t="n"/>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="n"/>
-      <c r="X19" s="7" t="n"/>
-      <c r="Y19" s="7" t="n"/>
-      <c r="Z19" s="7" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
     </row>
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -7029,12 +7078,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U20" s="7" t="n"/>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="n"/>
-      <c r="X20" s="7" t="n"/>
-      <c r="Y20" s="7" t="n"/>
-      <c r="Z20" s="7" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -7133,12 +7182,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U21" s="7" t="n"/>
-      <c r="V21" s="7" t="n"/>
-      <c r="W21" s="7" t="n"/>
-      <c r="X21" s="7" t="n"/>
-      <c r="Y21" s="7" t="n"/>
-      <c r="Z21" s="7" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
     </row>
     <row r="22" ht="75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -7237,12 +7286,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U22" s="7" t="n"/>
-      <c r="V22" s="7" t="n"/>
-      <c r="W22" s="7" t="n"/>
-      <c r="X22" s="7" t="n"/>
-      <c r="Y22" s="7" t="n"/>
-      <c r="Z22" s="7" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
     </row>
     <row r="23" ht="75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -7341,12 +7390,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U23" s="7" t="n"/>
-      <c r="V23" s="7" t="n"/>
-      <c r="W23" s="7" t="n"/>
-      <c r="X23" s="7" t="n"/>
-      <c r="Y23" s="7" t="n"/>
-      <c r="Z23" s="7" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
     </row>
     <row r="24" ht="75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -7445,12 +7494,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
-      <c r="Z24" s="7" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
+      <c r="Z24" s="6" t="n"/>
     </row>
     <row r="25" ht="75" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -7549,12 +7598,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U25" s="7" t="n"/>
-      <c r="V25" s="7" t="n"/>
-      <c r="W25" s="7" t="n"/>
-      <c r="X25" s="7" t="n"/>
-      <c r="Y25" s="7" t="n"/>
-      <c r="Z25" s="7" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
+      <c r="Z25" s="6" t="n"/>
     </row>
     <row r="26" ht="75" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -7651,12 +7700,12 @@
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="7" t="n"/>
-      <c r="V26" s="7" t="n"/>
-      <c r="W26" s="7" t="n"/>
-      <c r="X26" s="7" t="n"/>
-      <c r="Y26" s="7" t="n"/>
-      <c r="Z26" s="7" t="n"/>
+      <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
+      <c r="X26" s="6" t="n"/>
+      <c r="Y26" s="6" t="n"/>
+      <c r="Z26" s="6" t="n"/>
     </row>
     <row r="27" ht="75" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -7753,12 +7802,12 @@
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="7" t="n"/>
-      <c r="V27" s="7" t="n"/>
-      <c r="W27" s="7" t="n"/>
-      <c r="X27" s="7" t="n"/>
-      <c r="Y27" s="7" t="n"/>
-      <c r="Z27" s="7" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="6" t="n"/>
+      <c r="Z27" s="6" t="n"/>
     </row>
     <row r="28" ht="75" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -7857,12 +7906,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U28" s="7" t="n"/>
-      <c r="V28" s="7" t="n"/>
-      <c r="W28" s="7" t="n"/>
-      <c r="X28" s="7" t="n"/>
-      <c r="Y28" s="7" t="n"/>
-      <c r="Z28" s="7" t="n"/>
+      <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
+      <c r="X28" s="6" t="n"/>
+      <c r="Y28" s="6" t="n"/>
+      <c r="Z28" s="6" t="n"/>
     </row>
     <row r="29" ht="75" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -7961,12 +8010,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U29" s="7" t="n"/>
-      <c r="V29" s="7" t="n"/>
-      <c r="W29" s="7" t="n"/>
-      <c r="X29" s="7" t="n"/>
-      <c r="Y29" s="7" t="n"/>
-      <c r="Z29" s="7" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
+      <c r="Z29" s="6" t="n"/>
     </row>
     <row r="30" ht="75" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -8057,12 +8106,12 @@
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="7" t="n"/>
-      <c r="V30" s="7" t="n"/>
-      <c r="W30" s="7" t="n"/>
-      <c r="X30" s="7" t="n"/>
-      <c r="Y30" s="7" t="n"/>
-      <c r="Z30" s="7" t="n"/>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
+      <c r="X30" s="6" t="n"/>
+      <c r="Y30" s="6" t="n"/>
+      <c r="Z30" s="6" t="n"/>
     </row>
     <row r="31" ht="75" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -8157,12 +8206,12 @@
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr"/>
-      <c r="U31" s="7" t="n"/>
-      <c r="V31" s="7" t="n"/>
-      <c r="W31" s="7" t="n"/>
-      <c r="X31" s="7" t="n"/>
-      <c r="Y31" s="7" t="n"/>
-      <c r="Z31" s="7" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="6" t="n"/>
+      <c r="Z31" s="6" t="n"/>
     </row>
     <row r="32" ht="75" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -8257,12 +8306,12 @@
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="7" t="n"/>
-      <c r="V32" s="7" t="n"/>
-      <c r="W32" s="7" t="n"/>
-      <c r="X32" s="7" t="n"/>
-      <c r="Y32" s="7" t="n"/>
-      <c r="Z32" s="7" t="n"/>
+      <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
+      <c r="X32" s="6" t="n"/>
+      <c r="Y32" s="6" t="n"/>
+      <c r="Z32" s="6" t="n"/>
     </row>
     <row r="33" ht="75" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -8353,12 +8402,12 @@
       </c>
       <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="7" t="n"/>
-      <c r="V33" s="7" t="n"/>
-      <c r="W33" s="7" t="n"/>
-      <c r="X33" s="7" t="n"/>
-      <c r="Y33" s="7" t="n"/>
-      <c r="Z33" s="7" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="6" t="n"/>
+      <c r="Z33" s="6" t="n"/>
     </row>
     <row r="34" ht="75" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -8449,12 +8498,12 @@
       </c>
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="7" t="n"/>
-      <c r="V34" s="7" t="n"/>
-      <c r="W34" s="7" t="n"/>
-      <c r="X34" s="7" t="n"/>
-      <c r="Y34" s="7" t="n"/>
-      <c r="Z34" s="7" t="n"/>
+      <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="6" t="n"/>
+      <c r="Z34" s="6" t="n"/>
     </row>
     <row r="35" ht="75" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -8545,12 +8594,12 @@
       </c>
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="7" t="n"/>
-      <c r="V35" s="7" t="n"/>
-      <c r="W35" s="7" t="n"/>
-      <c r="X35" s="7" t="n"/>
-      <c r="Y35" s="7" t="n"/>
-      <c r="Z35" s="7" t="n"/>
+      <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="6" t="n"/>
+      <c r="Z35" s="6" t="n"/>
     </row>
     <row r="36" ht="75" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -8649,12 +8698,12 @@
           <t>Класс герметичности по ГОСТ 9544-2015 «А»</t>
         </is>
       </c>
-      <c r="U36" s="7" t="n"/>
-      <c r="V36" s="7" t="n"/>
-      <c r="W36" s="7" t="n"/>
-      <c r="X36" s="7" t="n"/>
-      <c r="Y36" s="7" t="n"/>
-      <c r="Z36" s="7" t="n"/>
+      <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
+      <c r="X36" s="6" t="n"/>
+      <c r="Y36" s="6" t="n"/>
+      <c r="Z36" s="6" t="n"/>
     </row>
     <row r="37" ht="75" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -8751,12 +8800,12 @@
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="7" t="n"/>
-      <c r="V37" s="7" t="n"/>
-      <c r="W37" s="7" t="n"/>
-      <c r="X37" s="7" t="n"/>
-      <c r="Y37" s="7" t="n"/>
-      <c r="Z37" s="7" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="6" t="n"/>
+      <c r="Z37" s="6" t="n"/>
     </row>
     <row r="38" ht="75" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -8855,12 +8904,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U38" s="7" t="n"/>
-      <c r="V38" s="7" t="n"/>
-      <c r="W38" s="7" t="n"/>
-      <c r="X38" s="7" t="n"/>
-      <c r="Y38" s="7" t="n"/>
-      <c r="Z38" s="7" t="n"/>
+      <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
+      <c r="X38" s="6" t="n"/>
+      <c r="Y38" s="6" t="n"/>
+      <c r="Z38" s="6" t="n"/>
     </row>
     <row r="39" ht="75" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -8955,12 +9004,12 @@
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="7" t="n"/>
-      <c r="V39" s="7" t="n"/>
-      <c r="W39" s="7" t="n"/>
-      <c r="X39" s="7" t="n"/>
-      <c r="Y39" s="7" t="n"/>
-      <c r="Z39" s="7" t="n"/>
+      <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
+      <c r="X39" s="6" t="n"/>
+      <c r="Y39" s="6" t="n"/>
+      <c r="Z39" s="6" t="n"/>
     </row>
     <row r="40" ht="75" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -9055,12 +9104,12 @@
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="7" t="n"/>
-      <c r="V40" s="7" t="n"/>
-      <c r="W40" s="7" t="n"/>
-      <c r="X40" s="7" t="n"/>
-      <c r="Y40" s="7" t="n"/>
-      <c r="Z40" s="7" t="n"/>
+      <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
+      <c r="X40" s="6" t="n"/>
+      <c r="Y40" s="6" t="n"/>
+      <c r="Z40" s="6" t="n"/>
     </row>
     <row r="41" ht="75" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -9155,12 +9204,12 @@
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="7" t="n"/>
-      <c r="V41" s="7" t="n"/>
-      <c r="W41" s="7" t="n"/>
-      <c r="X41" s="7" t="n"/>
-      <c r="Y41" s="7" t="n"/>
-      <c r="Z41" s="7" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="6" t="n"/>
+      <c r="Z41" s="6" t="n"/>
     </row>
     <row r="42" ht="75" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -9260,12 +9309,12 @@
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="7" t="n"/>
-      <c r="V42" s="7" t="n"/>
-      <c r="W42" s="7" t="n"/>
-      <c r="X42" s="7" t="n"/>
-      <c r="Y42" s="7" t="n"/>
-      <c r="Z42" s="7" t="n"/>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
+      <c r="X42" s="6" t="n"/>
+      <c r="Y42" s="6" t="n"/>
+      <c r="Z42" s="6" t="n"/>
     </row>
     <row r="43" ht="75" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -9364,12 +9413,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U43" s="7" t="n"/>
-      <c r="V43" s="7" t="n"/>
-      <c r="W43" s="7" t="n"/>
-      <c r="X43" s="7" t="n"/>
-      <c r="Y43" s="7" t="n"/>
-      <c r="Z43" s="7" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
+      <c r="X43" s="6" t="n"/>
+      <c r="Y43" s="6" t="n"/>
+      <c r="Z43" s="6" t="n"/>
     </row>
     <row r="44" ht="75" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -9468,12 +9517,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U44" s="7" t="n"/>
-      <c r="V44" s="7" t="n"/>
-      <c r="W44" s="7" t="n"/>
-      <c r="X44" s="7" t="n"/>
-      <c r="Y44" s="7" t="n"/>
-      <c r="Z44" s="7" t="n"/>
+      <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
+      <c r="X44" s="6" t="n"/>
+      <c r="Y44" s="6" t="n"/>
+      <c r="Z44" s="6" t="n"/>
     </row>
     <row r="45" ht="75" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -9572,12 +9621,12 @@
           <t>КРАН  УНИВЕРСАЛЬНОЙ СЕРИИ</t>
         </is>
       </c>
-      <c r="U45" s="7" t="n"/>
-      <c r="V45" s="7" t="n"/>
-      <c r="W45" s="7" t="n"/>
-      <c r="X45" s="7" t="n"/>
-      <c r="Y45" s="7" t="n"/>
-      <c r="Z45" s="7" t="n"/>
+      <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
+      <c r="X45" s="6" t="n"/>
+      <c r="Y45" s="6" t="n"/>
+      <c r="Z45" s="6" t="n"/>
     </row>
     <row r="46" ht="75" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -9672,12 +9721,12 @@
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="7" t="n"/>
-      <c r="V46" s="7" t="n"/>
-      <c r="W46" s="7" t="n"/>
-      <c r="X46" s="7" t="n"/>
-      <c r="Y46" s="7" t="n"/>
-      <c r="Z46" s="7" t="n"/>
+      <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
+      <c r="X46" s="6" t="n"/>
+      <c r="Y46" s="6" t="n"/>
+      <c r="Z46" s="6" t="n"/>
     </row>
     <row r="47" ht="75" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -9772,12 +9821,12 @@
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="7" t="n"/>
-      <c r="V47" s="7" t="n"/>
-      <c r="W47" s="7" t="n"/>
-      <c r="X47" s="7" t="n"/>
-      <c r="Y47" s="7" t="n"/>
-      <c r="Z47" s="7" t="n"/>
+      <c r="U47" s="6" t="n"/>
+      <c r="V47" s="6" t="n"/>
+      <c r="W47" s="6" t="n"/>
+      <c r="X47" s="6" t="n"/>
+      <c r="Y47" s="6" t="n"/>
+      <c r="Z47" s="6" t="n"/>
     </row>
     <row r="48" ht="75" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -9872,12 +9921,12 @@
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="7" t="n"/>
-      <c r="V48" s="7" t="n"/>
-      <c r="W48" s="7" t="n"/>
-      <c r="X48" s="7" t="n"/>
-      <c r="Y48" s="7" t="n"/>
-      <c r="Z48" s="7" t="n"/>
+      <c r="U48" s="6" t="n"/>
+      <c r="V48" s="6" t="n"/>
+      <c r="W48" s="6" t="n"/>
+      <c r="X48" s="6" t="n"/>
+      <c r="Y48" s="6" t="n"/>
+      <c r="Z48" s="6" t="n"/>
     </row>
     <row r="49" ht="75" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -9972,12 +10021,12 @@
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="7" t="n"/>
-      <c r="V49" s="7" t="n"/>
-      <c r="W49" s="7" t="n"/>
-      <c r="X49" s="7" t="n"/>
-      <c r="Y49" s="7" t="n"/>
-      <c r="Z49" s="7" t="n"/>
+      <c r="U49" s="6" t="n"/>
+      <c r="V49" s="6" t="n"/>
+      <c r="W49" s="6" t="n"/>
+      <c r="X49" s="6" t="n"/>
+      <c r="Y49" s="6" t="n"/>
+      <c r="Z49" s="6" t="n"/>
     </row>
     <row r="50" ht="75" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -10071,12 +10120,12 @@
       </c>
       <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="7" t="n"/>
-      <c r="V50" s="7" t="n"/>
-      <c r="W50" s="7" t="n"/>
-      <c r="X50" s="7" t="n"/>
-      <c r="Y50" s="7" t="n"/>
-      <c r="Z50" s="7" t="n"/>
+      <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
+      <c r="X50" s="6" t="n"/>
+      <c r="Y50" s="6" t="n"/>
+      <c r="Z50" s="6" t="n"/>
     </row>
     <row r="51" ht="75" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -10163,12 +10212,12 @@
       </c>
       <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="7" t="n"/>
-      <c r="V51" s="7" t="n"/>
-      <c r="W51" s="7" t="n"/>
-      <c r="X51" s="7" t="n"/>
-      <c r="Y51" s="7" t="n"/>
-      <c r="Z51" s="7" t="n"/>
+      <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
+      <c r="X51" s="6" t="n"/>
+      <c r="Y51" s="6" t="n"/>
+      <c r="Z51" s="6" t="n"/>
     </row>
     <row r="52" ht="75" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -10263,12 +10312,12 @@
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="7" t="n"/>
-      <c r="V52" s="7" t="n"/>
-      <c r="W52" s="7" t="n"/>
-      <c r="X52" s="7" t="n"/>
-      <c r="Y52" s="7" t="n"/>
-      <c r="Z52" s="7" t="n"/>
+      <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
+      <c r="X52" s="6" t="n"/>
+      <c r="Y52" s="6" t="n"/>
+      <c r="Z52" s="6" t="n"/>
     </row>
     <row r="53" ht="75" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -10362,12 +10411,12 @@
       </c>
       <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="7" t="n"/>
-      <c r="V53" s="7" t="n"/>
-      <c r="W53" s="7" t="n"/>
-      <c r="X53" s="7" t="n"/>
-      <c r="Y53" s="7" t="n"/>
-      <c r="Z53" s="7" t="n"/>
+      <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
+      <c r="X53" s="6" t="n"/>
+      <c r="Y53" s="6" t="n"/>
+      <c r="Z53" s="6" t="n"/>
     </row>
     <row r="54" ht="75" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -10462,12 +10511,12 @@
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="7" t="n"/>
-      <c r="V54" s="7" t="n"/>
-      <c r="W54" s="7" t="n"/>
-      <c r="X54" s="7" t="n"/>
-      <c r="Y54" s="7" t="n"/>
-      <c r="Z54" s="7" t="n"/>
+      <c r="U54" s="6" t="n"/>
+      <c r="V54" s="6" t="n"/>
+      <c r="W54" s="6" t="n"/>
+      <c r="X54" s="6" t="n"/>
+      <c r="Y54" s="6" t="n"/>
+      <c r="Z54" s="6" t="n"/>
     </row>
     <row r="55" ht="75" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -10562,12 +10611,12 @@
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="7" t="n"/>
-      <c r="V55" s="7" t="n"/>
-      <c r="W55" s="7" t="n"/>
-      <c r="X55" s="7" t="n"/>
-      <c r="Y55" s="7" t="n"/>
-      <c r="Z55" s="7" t="n"/>
+      <c r="U55" s="6" t="n"/>
+      <c r="V55" s="6" t="n"/>
+      <c r="W55" s="6" t="n"/>
+      <c r="X55" s="6" t="n"/>
+      <c r="Y55" s="6" t="n"/>
+      <c r="Z55" s="6" t="n"/>
     </row>
     <row r="56" ht="75" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -10662,12 +10711,12 @@
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="7" t="n"/>
-      <c r="V56" s="7" t="n"/>
-      <c r="W56" s="7" t="n"/>
-      <c r="X56" s="7" t="n"/>
-      <c r="Y56" s="7" t="n"/>
-      <c r="Z56" s="7" t="n"/>
+      <c r="U56" s="6" t="n"/>
+      <c r="V56" s="6" t="n"/>
+      <c r="W56" s="6" t="n"/>
+      <c r="X56" s="6" t="n"/>
+      <c r="Y56" s="6" t="n"/>
+      <c r="Z56" s="6" t="n"/>
     </row>
     <row r="57" ht="75" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -10762,12 +10811,12 @@
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="7" t="n"/>
-      <c r="V57" s="7" t="n"/>
-      <c r="W57" s="7" t="n"/>
-      <c r="X57" s="7" t="n"/>
-      <c r="Y57" s="7" t="n"/>
-      <c r="Z57" s="7" t="n"/>
+      <c r="U57" s="6" t="n"/>
+      <c r="V57" s="6" t="n"/>
+      <c r="W57" s="6" t="n"/>
+      <c r="X57" s="6" t="n"/>
+      <c r="Y57" s="6" t="n"/>
+      <c r="Z57" s="6" t="n"/>
     </row>
     <row r="58" ht="75" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -10862,12 +10911,12 @@
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="7" t="n"/>
-      <c r="V58" s="7" t="n"/>
-      <c r="W58" s="7" t="n"/>
-      <c r="X58" s="7" t="n"/>
-      <c r="Y58" s="7" t="n"/>
-      <c r="Z58" s="7" t="n"/>
+      <c r="U58" s="6" t="n"/>
+      <c r="V58" s="6" t="n"/>
+      <c r="W58" s="6" t="n"/>
+      <c r="X58" s="6" t="n"/>
+      <c r="Y58" s="6" t="n"/>
+      <c r="Z58" s="6" t="n"/>
     </row>
     <row r="59" ht="75" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -10962,12 +11011,12 @@
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="7" t="n"/>
-      <c r="V59" s="7" t="n"/>
-      <c r="W59" s="7" t="n"/>
-      <c r="X59" s="7" t="n"/>
-      <c r="Y59" s="7" t="n"/>
-      <c r="Z59" s="7" t="n"/>
+      <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
+      <c r="X59" s="6" t="n"/>
+      <c r="Y59" s="6" t="n"/>
+      <c r="Z59" s="6" t="n"/>
     </row>
     <row r="60" ht="75" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -11062,12 +11111,12 @@
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="7" t="n"/>
-      <c r="V60" s="7" t="n"/>
-      <c r="W60" s="7" t="n"/>
-      <c r="X60" s="7" t="n"/>
-      <c r="Y60" s="7" t="n"/>
-      <c r="Z60" s="7" t="n"/>
+      <c r="U60" s="6" t="n"/>
+      <c r="V60" s="6" t="n"/>
+      <c r="W60" s="6" t="n"/>
+      <c r="X60" s="6" t="n"/>
+      <c r="Y60" s="6" t="n"/>
+      <c r="Z60" s="6" t="n"/>
     </row>
     <row r="61" ht="75" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -11162,12 +11211,12 @@
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="7" t="n"/>
-      <c r="V61" s="7" t="n"/>
-      <c r="W61" s="7" t="n"/>
-      <c r="X61" s="7" t="n"/>
-      <c r="Y61" s="7" t="n"/>
-      <c r="Z61" s="7" t="n"/>
+      <c r="U61" s="6" t="n"/>
+      <c r="V61" s="6" t="n"/>
+      <c r="W61" s="6" t="n"/>
+      <c r="X61" s="6" t="n"/>
+      <c r="Y61" s="6" t="n"/>
+      <c r="Z61" s="6" t="n"/>
     </row>
     <row r="62" ht="75" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -11262,12 +11311,12 @@
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="7" t="n"/>
-      <c r="V62" s="7" t="n"/>
-      <c r="W62" s="7" t="n"/>
-      <c r="X62" s="7" t="n"/>
-      <c r="Y62" s="7" t="n"/>
-      <c r="Z62" s="7" t="n"/>
+      <c r="U62" s="6" t="n"/>
+      <c r="V62" s="6" t="n"/>
+      <c r="W62" s="6" t="n"/>
+      <c r="X62" s="6" t="n"/>
+      <c r="Y62" s="6" t="n"/>
+      <c r="Z62" s="6" t="n"/>
     </row>
     <row r="63" ht="75" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -11362,12 +11411,12 @@
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="7" t="n"/>
-      <c r="V63" s="7" t="n"/>
-      <c r="W63" s="7" t="n"/>
-      <c r="X63" s="7" t="n"/>
-      <c r="Y63" s="7" t="n"/>
-      <c r="Z63" s="7" t="n"/>
+      <c r="U63" s="6" t="n"/>
+      <c r="V63" s="6" t="n"/>
+      <c r="W63" s="6" t="n"/>
+      <c r="X63" s="6" t="n"/>
+      <c r="Y63" s="6" t="n"/>
+      <c r="Z63" s="6" t="n"/>
     </row>
     <row r="64" ht="75" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -11467,12 +11516,12 @@
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="7" t="n"/>
-      <c r="V64" s="7" t="n"/>
-      <c r="W64" s="7" t="n"/>
-      <c r="X64" s="7" t="n"/>
-      <c r="Y64" s="7" t="n"/>
-      <c r="Z64" s="7" t="n"/>
+      <c r="U64" s="6" t="n"/>
+      <c r="V64" s="6" t="n"/>
+      <c r="W64" s="6" t="n"/>
+      <c r="X64" s="6" t="n"/>
+      <c r="Y64" s="6" t="n"/>
+      <c r="Z64" s="6" t="n"/>
     </row>
     <row r="65" ht="75" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -11572,12 +11621,12 @@
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr"/>
-      <c r="U65" s="7" t="n"/>
-      <c r="V65" s="7" t="n"/>
-      <c r="W65" s="7" t="n"/>
-      <c r="X65" s="7" t="n"/>
-      <c r="Y65" s="7" t="n"/>
-      <c r="Z65" s="7" t="n"/>
+      <c r="U65" s="6" t="n"/>
+      <c r="V65" s="6" t="n"/>
+      <c r="W65" s="6" t="n"/>
+      <c r="X65" s="6" t="n"/>
+      <c r="Y65" s="6" t="n"/>
+      <c r="Z65" s="6" t="n"/>
     </row>
     <row r="66" ht="75" customHeight="1">
       <c r="A66" s="3" t="n">
@@ -11677,12 +11726,12 @@
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr"/>
-      <c r="U66" s="7" t="n"/>
-      <c r="V66" s="7" t="n"/>
-      <c r="W66" s="7" t="n"/>
-      <c r="X66" s="7" t="n"/>
-      <c r="Y66" s="7" t="n"/>
-      <c r="Z66" s="7" t="n"/>
+      <c r="U66" s="6" t="n"/>
+      <c r="V66" s="6" t="n"/>
+      <c r="W66" s="6" t="n"/>
+      <c r="X66" s="6" t="n"/>
+      <c r="Y66" s="6" t="n"/>
+      <c r="Z66" s="6" t="n"/>
     </row>
     <row r="67" ht="75" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -11782,12 +11831,12 @@
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr"/>
-      <c r="U67" s="7" t="n"/>
-      <c r="V67" s="7" t="n"/>
-      <c r="W67" s="7" t="n"/>
-      <c r="X67" s="7" t="n"/>
-      <c r="Y67" s="7" t="n"/>
-      <c r="Z67" s="7" t="n"/>
+      <c r="U67" s="6" t="n"/>
+      <c r="V67" s="6" t="n"/>
+      <c r="W67" s="6" t="n"/>
+      <c r="X67" s="6" t="n"/>
+      <c r="Y67" s="6" t="n"/>
+      <c r="Z67" s="6" t="n"/>
     </row>
     <row r="68" ht="75" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -11878,12 +11927,12 @@
       </c>
       <c r="S68" s="3" t="inlineStr"/>
       <c r="T68" s="3" t="inlineStr"/>
-      <c r="U68" s="7" t="n"/>
-      <c r="V68" s="7" t="n"/>
-      <c r="W68" s="7" t="n"/>
-      <c r="X68" s="7" t="n"/>
-      <c r="Y68" s="7" t="n"/>
-      <c r="Z68" s="7" t="n"/>
+      <c r="U68" s="6" t="n"/>
+      <c r="V68" s="6" t="n"/>
+      <c r="W68" s="6" t="n"/>
+      <c r="X68" s="6" t="n"/>
+      <c r="Y68" s="6" t="n"/>
+      <c r="Z68" s="6" t="n"/>
     </row>
     <row r="69" ht="75" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -11974,12 +12023,12 @@
       </c>
       <c r="S69" s="3" t="inlineStr"/>
       <c r="T69" s="3" t="inlineStr"/>
-      <c r="U69" s="7" t="n"/>
-      <c r="V69" s="7" t="n"/>
-      <c r="W69" s="7" t="n"/>
-      <c r="X69" s="7" t="n"/>
-      <c r="Y69" s="7" t="n"/>
-      <c r="Z69" s="7" t="n"/>
+      <c r="U69" s="6" t="n"/>
+      <c r="V69" s="6" t="n"/>
+      <c r="W69" s="6" t="n"/>
+      <c r="X69" s="6" t="n"/>
+      <c r="Y69" s="6" t="n"/>
+      <c r="Z69" s="6" t="n"/>
     </row>
     <row r="70" ht="75" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -12070,12 +12119,12 @@
       </c>
       <c r="S70" s="3" t="inlineStr"/>
       <c r="T70" s="3" t="inlineStr"/>
-      <c r="U70" s="7" t="n"/>
-      <c r="V70" s="7" t="n"/>
-      <c r="W70" s="7" t="n"/>
-      <c r="X70" s="7" t="n"/>
-      <c r="Y70" s="7" t="n"/>
-      <c r="Z70" s="7" t="n"/>
+      <c r="U70" s="6" t="n"/>
+      <c r="V70" s="6" t="n"/>
+      <c r="W70" s="6" t="n"/>
+      <c r="X70" s="6" t="n"/>
+      <c r="Y70" s="6" t="n"/>
+      <c r="Z70" s="6" t="n"/>
     </row>
     <row r="71" ht="75" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -12166,12 +12215,12 @@
       </c>
       <c r="S71" s="3" t="inlineStr"/>
       <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="7" t="n"/>
-      <c r="V71" s="7" t="n"/>
-      <c r="W71" s="7" t="n"/>
-      <c r="X71" s="7" t="n"/>
-      <c r="Y71" s="7" t="n"/>
-      <c r="Z71" s="7" t="n"/>
+      <c r="U71" s="6" t="n"/>
+      <c r="V71" s="6" t="n"/>
+      <c r="W71" s="6" t="n"/>
+      <c r="X71" s="6" t="n"/>
+      <c r="Y71" s="6" t="n"/>
+      <c r="Z71" s="6" t="n"/>
     </row>
     <row r="72" ht="75" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -12262,12 +12311,12 @@
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr"/>
-      <c r="U72" s="7" t="n"/>
-      <c r="V72" s="7" t="n"/>
-      <c r="W72" s="7" t="n"/>
-      <c r="X72" s="7" t="n"/>
-      <c r="Y72" s="7" t="n"/>
-      <c r="Z72" s="7" t="n"/>
+      <c r="U72" s="6" t="n"/>
+      <c r="V72" s="6" t="n"/>
+      <c r="W72" s="6" t="n"/>
+      <c r="X72" s="6" t="n"/>
+      <c r="Y72" s="6" t="n"/>
+      <c r="Z72" s="6" t="n"/>
     </row>
     <row r="73" ht="75" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -12362,12 +12411,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U73" s="7" t="n"/>
-      <c r="V73" s="7" t="n"/>
-      <c r="W73" s="7" t="n"/>
-      <c r="X73" s="7" t="n"/>
-      <c r="Y73" s="7" t="n"/>
-      <c r="Z73" s="7" t="n"/>
+      <c r="U73" s="6" t="n"/>
+      <c r="V73" s="6" t="n"/>
+      <c r="W73" s="6" t="n"/>
+      <c r="X73" s="6" t="n"/>
+      <c r="Y73" s="6" t="n"/>
+      <c r="Z73" s="6" t="n"/>
     </row>
     <row r="74" ht="75" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -12462,12 +12511,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U74" s="7" t="n"/>
-      <c r="V74" s="7" t="n"/>
-      <c r="W74" s="7" t="n"/>
-      <c r="X74" s="7" t="n"/>
-      <c r="Y74" s="7" t="n"/>
-      <c r="Z74" s="7" t="n"/>
+      <c r="U74" s="6" t="n"/>
+      <c r="V74" s="6" t="n"/>
+      <c r="W74" s="6" t="n"/>
+      <c r="X74" s="6" t="n"/>
+      <c r="Y74" s="6" t="n"/>
+      <c r="Z74" s="6" t="n"/>
     </row>
     <row r="75" ht="75" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -12562,12 +12611,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U75" s="7" t="n"/>
-      <c r="V75" s="7" t="n"/>
-      <c r="W75" s="7" t="n"/>
-      <c r="X75" s="7" t="n"/>
-      <c r="Y75" s="7" t="n"/>
-      <c r="Z75" s="7" t="n"/>
+      <c r="U75" s="6" t="n"/>
+      <c r="V75" s="6" t="n"/>
+      <c r="W75" s="6" t="n"/>
+      <c r="X75" s="6" t="n"/>
+      <c r="Y75" s="6" t="n"/>
+      <c r="Z75" s="6" t="n"/>
     </row>
     <row r="76" ht="75" customHeight="1">
       <c r="A76" s="3" t="n">
@@ -12658,12 +12707,12 @@
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr"/>
-      <c r="U76" s="7" t="n"/>
-      <c r="V76" s="7" t="n"/>
-      <c r="W76" s="7" t="n"/>
-      <c r="X76" s="7" t="n"/>
-      <c r="Y76" s="7" t="n"/>
-      <c r="Z76" s="7" t="n"/>
+      <c r="U76" s="6" t="n"/>
+      <c r="V76" s="6" t="n"/>
+      <c r="W76" s="6" t="n"/>
+      <c r="X76" s="6" t="n"/>
+      <c r="Y76" s="6" t="n"/>
+      <c r="Z76" s="6" t="n"/>
     </row>
     <row r="77" ht="75" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -12754,12 +12803,12 @@
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr"/>
-      <c r="U77" s="7" t="n"/>
-      <c r="V77" s="7" t="n"/>
-      <c r="W77" s="7" t="n"/>
-      <c r="X77" s="7" t="n"/>
-      <c r="Y77" s="7" t="n"/>
-      <c r="Z77" s="7" t="n"/>
+      <c r="U77" s="6" t="n"/>
+      <c r="V77" s="6" t="n"/>
+      <c r="W77" s="6" t="n"/>
+      <c r="X77" s="6" t="n"/>
+      <c r="Y77" s="6" t="n"/>
+      <c r="Z77" s="6" t="n"/>
     </row>
     <row r="78" ht="75" customHeight="1">
       <c r="A78" s="3" t="n">
@@ -12850,12 +12899,12 @@
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr"/>
-      <c r="U78" s="7" t="n"/>
-      <c r="V78" s="7" t="n"/>
-      <c r="W78" s="7" t="n"/>
-      <c r="X78" s="7" t="n"/>
-      <c r="Y78" s="7" t="n"/>
-      <c r="Z78" s="7" t="n"/>
+      <c r="U78" s="6" t="n"/>
+      <c r="V78" s="6" t="n"/>
+      <c r="W78" s="6" t="n"/>
+      <c r="X78" s="6" t="n"/>
+      <c r="Y78" s="6" t="n"/>
+      <c r="Z78" s="6" t="n"/>
     </row>
     <row r="79" ht="75" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -12946,12 +12995,12 @@
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr"/>
-      <c r="U79" s="7" t="n"/>
-      <c r="V79" s="7" t="n"/>
-      <c r="W79" s="7" t="n"/>
-      <c r="X79" s="7" t="n"/>
-      <c r="Y79" s="7" t="n"/>
-      <c r="Z79" s="7" t="n"/>
+      <c r="U79" s="6" t="n"/>
+      <c r="V79" s="6" t="n"/>
+      <c r="W79" s="6" t="n"/>
+      <c r="X79" s="6" t="n"/>
+      <c r="Y79" s="6" t="n"/>
+      <c r="Z79" s="6" t="n"/>
     </row>
     <row r="80" ht="75" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -13042,12 +13091,12 @@
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr"/>
-      <c r="U80" s="7" t="n"/>
-      <c r="V80" s="7" t="n"/>
-      <c r="W80" s="7" t="n"/>
-      <c r="X80" s="7" t="n"/>
-      <c r="Y80" s="7" t="n"/>
-      <c r="Z80" s="7" t="n"/>
+      <c r="U80" s="6" t="n"/>
+      <c r="V80" s="6" t="n"/>
+      <c r="W80" s="6" t="n"/>
+      <c r="X80" s="6" t="n"/>
+      <c r="Y80" s="6" t="n"/>
+      <c r="Z80" s="6" t="n"/>
     </row>
     <row r="81" ht="75" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -13138,12 +13187,12 @@
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr"/>
-      <c r="U81" s="7" t="n"/>
-      <c r="V81" s="7" t="n"/>
-      <c r="W81" s="7" t="n"/>
-      <c r="X81" s="7" t="n"/>
-      <c r="Y81" s="7" t="n"/>
-      <c r="Z81" s="7" t="n"/>
+      <c r="U81" s="6" t="n"/>
+      <c r="V81" s="6" t="n"/>
+      <c r="W81" s="6" t="n"/>
+      <c r="X81" s="6" t="n"/>
+      <c r="Y81" s="6" t="n"/>
+      <c r="Z81" s="6" t="n"/>
     </row>
     <row r="82" ht="75" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -13234,12 +13283,12 @@
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr"/>
-      <c r="U82" s="7" t="n"/>
-      <c r="V82" s="7" t="n"/>
-      <c r="W82" s="7" t="n"/>
-      <c r="X82" s="7" t="n"/>
-      <c r="Y82" s="7" t="n"/>
-      <c r="Z82" s="7" t="n"/>
+      <c r="U82" s="6" t="n"/>
+      <c r="V82" s="6" t="n"/>
+      <c r="W82" s="6" t="n"/>
+      <c r="X82" s="6" t="n"/>
+      <c r="Y82" s="6" t="n"/>
+      <c r="Z82" s="6" t="n"/>
     </row>
     <row r="83" ht="75" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -13326,12 +13375,12 @@
         </is>
       </c>
       <c r="T83" s="3" t="inlineStr"/>
-      <c r="U83" s="7" t="n"/>
-      <c r="V83" s="7" t="n"/>
-      <c r="W83" s="7" t="n"/>
-      <c r="X83" s="7" t="n"/>
-      <c r="Y83" s="7" t="n"/>
-      <c r="Z83" s="7" t="n"/>
+      <c r="U83" s="6" t="n"/>
+      <c r="V83" s="6" t="n"/>
+      <c r="W83" s="6" t="n"/>
+      <c r="X83" s="6" t="n"/>
+      <c r="Y83" s="6" t="n"/>
+      <c r="Z83" s="6" t="n"/>
     </row>
     <row r="84" ht="75" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -13430,12 +13479,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U84" s="7" t="n"/>
-      <c r="V84" s="7" t="n"/>
-      <c r="W84" s="7" t="n"/>
-      <c r="X84" s="7" t="n"/>
-      <c r="Y84" s="7" t="n"/>
-      <c r="Z84" s="7" t="n"/>
+      <c r="U84" s="6" t="n"/>
+      <c r="V84" s="6" t="n"/>
+      <c r="W84" s="6" t="n"/>
+      <c r="X84" s="6" t="n"/>
+      <c r="Y84" s="6" t="n"/>
+      <c r="Z84" s="6" t="n"/>
     </row>
     <row r="85" ht="75" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -13534,12 +13583,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U85" s="7" t="n"/>
-      <c r="V85" s="7" t="n"/>
-      <c r="W85" s="7" t="n"/>
-      <c r="X85" s="7" t="n"/>
-      <c r="Y85" s="7" t="n"/>
-      <c r="Z85" s="7" t="n"/>
+      <c r="U85" s="6" t="n"/>
+      <c r="V85" s="6" t="n"/>
+      <c r="W85" s="6" t="n"/>
+      <c r="X85" s="6" t="n"/>
+      <c r="Y85" s="6" t="n"/>
+      <c r="Z85" s="6" t="n"/>
     </row>
     <row r="86" ht="75" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -13638,12 +13687,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U86" s="7" t="n"/>
-      <c r="V86" s="7" t="n"/>
-      <c r="W86" s="7" t="n"/>
-      <c r="X86" s="7" t="n"/>
-      <c r="Y86" s="7" t="n"/>
-      <c r="Z86" s="7" t="n"/>
+      <c r="U86" s="6" t="n"/>
+      <c r="V86" s="6" t="n"/>
+      <c r="W86" s="6" t="n"/>
+      <c r="X86" s="6" t="n"/>
+      <c r="Y86" s="6" t="n"/>
+      <c r="Z86" s="6" t="n"/>
     </row>
     <row r="87" ht="75" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -13737,12 +13786,12 @@
       </c>
       <c r="S87" s="3" t="inlineStr"/>
       <c r="T87" s="3" t="inlineStr"/>
-      <c r="U87" s="7" t="n"/>
-      <c r="V87" s="7" t="n"/>
-      <c r="W87" s="7" t="n"/>
-      <c r="X87" s="7" t="n"/>
-      <c r="Y87" s="7" t="n"/>
-      <c r="Z87" s="7" t="n"/>
+      <c r="U87" s="6" t="n"/>
+      <c r="V87" s="6" t="n"/>
+      <c r="W87" s="6" t="n"/>
+      <c r="X87" s="6" t="n"/>
+      <c r="Y87" s="6" t="n"/>
+      <c r="Z87" s="6" t="n"/>
     </row>
     <row r="88" ht="75" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -13829,12 +13878,12 @@
       </c>
       <c r="S88" s="3" t="inlineStr"/>
       <c r="T88" s="3" t="inlineStr"/>
-      <c r="U88" s="7" t="n"/>
-      <c r="V88" s="7" t="n"/>
-      <c r="W88" s="7" t="n"/>
-      <c r="X88" s="7" t="n"/>
-      <c r="Y88" s="7" t="n"/>
-      <c r="Z88" s="7" t="n"/>
+      <c r="U88" s="6" t="n"/>
+      <c r="V88" s="6" t="n"/>
+      <c r="W88" s="6" t="n"/>
+      <c r="X88" s="6" t="n"/>
+      <c r="Y88" s="6" t="n"/>
+      <c r="Z88" s="6" t="n"/>
     </row>
     <row r="89" ht="75" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -13929,12 +13978,12 @@
         </is>
       </c>
       <c r="T89" s="3" t="inlineStr"/>
-      <c r="U89" s="7" t="n"/>
-      <c r="V89" s="7" t="n"/>
-      <c r="W89" s="7" t="n"/>
-      <c r="X89" s="7" t="n"/>
-      <c r="Y89" s="7" t="n"/>
-      <c r="Z89" s="7" t="n"/>
+      <c r="U89" s="6" t="n"/>
+      <c r="V89" s="6" t="n"/>
+      <c r="W89" s="6" t="n"/>
+      <c r="X89" s="6" t="n"/>
+      <c r="Y89" s="6" t="n"/>
+      <c r="Z89" s="6" t="n"/>
     </row>
     <row r="90" ht="75" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -14028,12 +14077,12 @@
       </c>
       <c r="S90" s="3" t="inlineStr"/>
       <c r="T90" s="3" t="inlineStr"/>
-      <c r="U90" s="7" t="n"/>
-      <c r="V90" s="7" t="n"/>
-      <c r="W90" s="7" t="n"/>
-      <c r="X90" s="7" t="n"/>
-      <c r="Y90" s="7" t="n"/>
-      <c r="Z90" s="7" t="n"/>
+      <c r="U90" s="6" t="n"/>
+      <c r="V90" s="6" t="n"/>
+      <c r="W90" s="6" t="n"/>
+      <c r="X90" s="6" t="n"/>
+      <c r="Y90" s="6" t="n"/>
+      <c r="Z90" s="6" t="n"/>
     </row>
     <row r="91" ht="75" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -14128,12 +14177,12 @@
         </is>
       </c>
       <c r="T91" s="3" t="inlineStr"/>
-      <c r="U91" s="7" t="n"/>
-      <c r="V91" s="7" t="n"/>
-      <c r="W91" s="7" t="n"/>
-      <c r="X91" s="7" t="n"/>
-      <c r="Y91" s="7" t="n"/>
-      <c r="Z91" s="7" t="n"/>
+      <c r="U91" s="6" t="n"/>
+      <c r="V91" s="6" t="n"/>
+      <c r="W91" s="6" t="n"/>
+      <c r="X91" s="6" t="n"/>
+      <c r="Y91" s="6" t="n"/>
+      <c r="Z91" s="6" t="n"/>
     </row>
     <row r="92" ht="75" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -14228,12 +14277,12 @@
         </is>
       </c>
       <c r="T92" s="3" t="inlineStr"/>
-      <c r="U92" s="7" t="n"/>
-      <c r="V92" s="7" t="n"/>
-      <c r="W92" s="7" t="n"/>
-      <c r="X92" s="7" t="n"/>
-      <c r="Y92" s="7" t="n"/>
-      <c r="Z92" s="7" t="n"/>
+      <c r="U92" s="6" t="n"/>
+      <c r="V92" s="6" t="n"/>
+      <c r="W92" s="6" t="n"/>
+      <c r="X92" s="6" t="n"/>
+      <c r="Y92" s="6" t="n"/>
+      <c r="Z92" s="6" t="n"/>
     </row>
     <row r="93" ht="75" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -14328,12 +14377,12 @@
         </is>
       </c>
       <c r="T93" s="3" t="inlineStr"/>
-      <c r="U93" s="7" t="n"/>
-      <c r="V93" s="7" t="n"/>
-      <c r="W93" s="7" t="n"/>
-      <c r="X93" s="7" t="n"/>
-      <c r="Y93" s="7" t="n"/>
-      <c r="Z93" s="7" t="n"/>
+      <c r="U93" s="6" t="n"/>
+      <c r="V93" s="6" t="n"/>
+      <c r="W93" s="6" t="n"/>
+      <c r="X93" s="6" t="n"/>
+      <c r="Y93" s="6" t="n"/>
+      <c r="Z93" s="6" t="n"/>
     </row>
     <row r="94" ht="75" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -14432,12 +14481,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U94" s="7" t="n"/>
-      <c r="V94" s="7" t="n"/>
-      <c r="W94" s="7" t="n"/>
-      <c r="X94" s="7" t="n"/>
-      <c r="Y94" s="7" t="n"/>
-      <c r="Z94" s="7" t="n"/>
+      <c r="U94" s="6" t="n"/>
+      <c r="V94" s="6" t="n"/>
+      <c r="W94" s="6" t="n"/>
+      <c r="X94" s="6" t="n"/>
+      <c r="Y94" s="6" t="n"/>
+      <c r="Z94" s="6" t="n"/>
     </row>
     <row r="95" ht="75" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -14536,12 +14585,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U95" s="7" t="n"/>
-      <c r="V95" s="7" t="n"/>
-      <c r="W95" s="7" t="n"/>
-      <c r="X95" s="7" t="n"/>
-      <c r="Y95" s="7" t="n"/>
-      <c r="Z95" s="7" t="n"/>
+      <c r="U95" s="6" t="n"/>
+      <c r="V95" s="6" t="n"/>
+      <c r="W95" s="6" t="n"/>
+      <c r="X95" s="6" t="n"/>
+      <c r="Y95" s="6" t="n"/>
+      <c r="Z95" s="6" t="n"/>
     </row>
     <row r="96" ht="75" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -14640,12 +14689,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U96" s="7" t="n"/>
-      <c r="V96" s="7" t="n"/>
-      <c r="W96" s="7" t="n"/>
-      <c r="X96" s="7" t="n"/>
-      <c r="Y96" s="7" t="n"/>
-      <c r="Z96" s="7" t="n"/>
+      <c r="U96" s="6" t="n"/>
+      <c r="V96" s="6" t="n"/>
+      <c r="W96" s="6" t="n"/>
+      <c r="X96" s="6" t="n"/>
+      <c r="Y96" s="6" t="n"/>
+      <c r="Z96" s="6" t="n"/>
     </row>
     <row r="97" ht="75" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -14744,12 +14793,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U97" s="7" t="n"/>
-      <c r="V97" s="7" t="n"/>
-      <c r="W97" s="7" t="n"/>
-      <c r="X97" s="7" t="n"/>
-      <c r="Y97" s="7" t="n"/>
-      <c r="Z97" s="7" t="n"/>
+      <c r="U97" s="6" t="n"/>
+      <c r="V97" s="6" t="n"/>
+      <c r="W97" s="6" t="n"/>
+      <c r="X97" s="6" t="n"/>
+      <c r="Y97" s="6" t="n"/>
+      <c r="Z97" s="6" t="n"/>
     </row>
     <row r="98" ht="75" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -14848,12 +14897,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U98" s="7" t="n"/>
-      <c r="V98" s="7" t="n"/>
-      <c r="W98" s="7" t="n"/>
-      <c r="X98" s="7" t="n"/>
-      <c r="Y98" s="7" t="n"/>
-      <c r="Z98" s="7" t="n"/>
+      <c r="U98" s="6" t="n"/>
+      <c r="V98" s="6" t="n"/>
+      <c r="W98" s="6" t="n"/>
+      <c r="X98" s="6" t="n"/>
+      <c r="Y98" s="6" t="n"/>
+      <c r="Z98" s="6" t="n"/>
     </row>
     <row r="99" ht="75" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -14952,12 +15001,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U99" s="7" t="n"/>
-      <c r="V99" s="7" t="n"/>
-      <c r="W99" s="7" t="n"/>
-      <c r="X99" s="7" t="n"/>
-      <c r="Y99" s="7" t="n"/>
-      <c r="Z99" s="7" t="n"/>
+      <c r="U99" s="6" t="n"/>
+      <c r="V99" s="6" t="n"/>
+      <c r="W99" s="6" t="n"/>
+      <c r="X99" s="6" t="n"/>
+      <c r="Y99" s="6" t="n"/>
+      <c r="Z99" s="6" t="n"/>
     </row>
     <row r="100" ht="75" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -15058,12 +15107,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U100" s="7" t="n"/>
-      <c r="V100" s="7" t="n"/>
-      <c r="W100" s="7" t="n"/>
-      <c r="X100" s="7" t="n"/>
-      <c r="Y100" s="7" t="n"/>
-      <c r="Z100" s="7" t="n"/>
+      <c r="U100" s="6" t="n"/>
+      <c r="V100" s="6" t="n"/>
+      <c r="W100" s="6" t="n"/>
+      <c r="X100" s="6" t="n"/>
+      <c r="Y100" s="6" t="n"/>
+      <c r="Z100" s="6" t="n"/>
     </row>
     <row r="101" ht="75" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -15164,12 +15213,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U101" s="7" t="n"/>
-      <c r="V101" s="7" t="n"/>
-      <c r="W101" s="7" t="n"/>
-      <c r="X101" s="7" t="n"/>
-      <c r="Y101" s="7" t="n"/>
-      <c r="Z101" s="7" t="n"/>
+      <c r="U101" s="6" t="n"/>
+      <c r="V101" s="6" t="n"/>
+      <c r="W101" s="6" t="n"/>
+      <c r="X101" s="6" t="n"/>
+      <c r="Y101" s="6" t="n"/>
+      <c r="Z101" s="6" t="n"/>
     </row>
     <row r="102" ht="75" customHeight="1">
       <c r="A102" s="3" t="n">
@@ -15270,12 +15319,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U102" s="7" t="n"/>
-      <c r="V102" s="7" t="n"/>
-      <c r="W102" s="7" t="n"/>
-      <c r="X102" s="7" t="n"/>
-      <c r="Y102" s="7" t="n"/>
-      <c r="Z102" s="7" t="n"/>
+      <c r="U102" s="6" t="n"/>
+      <c r="V102" s="6" t="n"/>
+      <c r="W102" s="6" t="n"/>
+      <c r="X102" s="6" t="n"/>
+      <c r="Y102" s="6" t="n"/>
+      <c r="Z102" s="6" t="n"/>
     </row>
     <row r="103" ht="75" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -15376,12 +15425,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U103" s="7" t="n"/>
-      <c r="V103" s="7" t="n"/>
-      <c r="W103" s="7" t="n"/>
-      <c r="X103" s="7" t="n"/>
-      <c r="Y103" s="7" t="n"/>
-      <c r="Z103" s="7" t="n"/>
+      <c r="U103" s="6" t="n"/>
+      <c r="V103" s="6" t="n"/>
+      <c r="W103" s="6" t="n"/>
+      <c r="X103" s="6" t="n"/>
+      <c r="Y103" s="6" t="n"/>
+      <c r="Z103" s="6" t="n"/>
     </row>
     <row r="104" ht="75" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -15482,12 +15531,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U104" s="7" t="n"/>
-      <c r="V104" s="7" t="n"/>
-      <c r="W104" s="7" t="n"/>
-      <c r="X104" s="7" t="n"/>
-      <c r="Y104" s="7" t="n"/>
-      <c r="Z104" s="7" t="n"/>
+      <c r="U104" s="6" t="n"/>
+      <c r="V104" s="6" t="n"/>
+      <c r="W104" s="6" t="n"/>
+      <c r="X104" s="6" t="n"/>
+      <c r="Y104" s="6" t="n"/>
+      <c r="Z104" s="6" t="n"/>
     </row>
     <row r="105" ht="75" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -15586,12 +15635,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U105" s="7" t="n"/>
-      <c r="V105" s="7" t="n"/>
-      <c r="W105" s="7" t="n"/>
-      <c r="X105" s="7" t="n"/>
-      <c r="Y105" s="7" t="n"/>
-      <c r="Z105" s="7" t="n"/>
+      <c r="U105" s="6" t="n"/>
+      <c r="V105" s="6" t="n"/>
+      <c r="W105" s="6" t="n"/>
+      <c r="X105" s="6" t="n"/>
+      <c r="Y105" s="6" t="n"/>
+      <c r="Z105" s="6" t="n"/>
     </row>
     <row r="106" ht="75" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -15690,12 +15739,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U106" s="7" t="n"/>
-      <c r="V106" s="7" t="n"/>
-      <c r="W106" s="7" t="n"/>
-      <c r="X106" s="7" t="n"/>
-      <c r="Y106" s="7" t="n"/>
-      <c r="Z106" s="7" t="n"/>
+      <c r="U106" s="6" t="n"/>
+      <c r="V106" s="6" t="n"/>
+      <c r="W106" s="6" t="n"/>
+      <c r="X106" s="6" t="n"/>
+      <c r="Y106" s="6" t="n"/>
+      <c r="Z106" s="6" t="n"/>
     </row>
     <row r="107" ht="75" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -15794,12 +15843,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U107" s="7" t="n"/>
-      <c r="V107" s="7" t="n"/>
-      <c r="W107" s="7" t="n"/>
-      <c r="X107" s="7" t="n"/>
-      <c r="Y107" s="7" t="n"/>
-      <c r="Z107" s="7" t="n"/>
+      <c r="U107" s="6" t="n"/>
+      <c r="V107" s="6" t="n"/>
+      <c r="W107" s="6" t="n"/>
+      <c r="X107" s="6" t="n"/>
+      <c r="Y107" s="6" t="n"/>
+      <c r="Z107" s="6" t="n"/>
     </row>
     <row r="108" ht="75" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -15901,12 +15950,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U108" s="7" t="n"/>
-      <c r="V108" s="7" t="n"/>
-      <c r="W108" s="7" t="n"/>
-      <c r="X108" s="7" t="n"/>
-      <c r="Y108" s="7" t="n"/>
-      <c r="Z108" s="7" t="n"/>
+      <c r="U108" s="6" t="n"/>
+      <c r="V108" s="6" t="n"/>
+      <c r="W108" s="6" t="n"/>
+      <c r="X108" s="6" t="n"/>
+      <c r="Y108" s="6" t="n"/>
+      <c r="Z108" s="6" t="n"/>
     </row>
     <row r="109" ht="75" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -16008,12 +16057,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U109" s="7" t="n"/>
-      <c r="V109" s="7" t="n"/>
-      <c r="W109" s="7" t="n"/>
-      <c r="X109" s="7" t="n"/>
-      <c r="Y109" s="7" t="n"/>
-      <c r="Z109" s="7" t="n"/>
+      <c r="U109" s="6" t="n"/>
+      <c r="V109" s="6" t="n"/>
+      <c r="W109" s="6" t="n"/>
+      <c r="X109" s="6" t="n"/>
+      <c r="Y109" s="6" t="n"/>
+      <c r="Z109" s="6" t="n"/>
     </row>
     <row r="110" ht="75" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -16115,12 +16164,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U110" s="7" t="n"/>
-      <c r="V110" s="7" t="n"/>
-      <c r="W110" s="7" t="n"/>
-      <c r="X110" s="7" t="n"/>
-      <c r="Y110" s="7" t="n"/>
-      <c r="Z110" s="7" t="n"/>
+      <c r="U110" s="6" t="n"/>
+      <c r="V110" s="6" t="n"/>
+      <c r="W110" s="6" t="n"/>
+      <c r="X110" s="6" t="n"/>
+      <c r="Y110" s="6" t="n"/>
+      <c r="Z110" s="6" t="n"/>
     </row>
     <row r="111" ht="75" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -16222,12 +16271,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U111" s="7" t="n"/>
-      <c r="V111" s="7" t="n"/>
-      <c r="W111" s="7" t="n"/>
-      <c r="X111" s="7" t="n"/>
-      <c r="Y111" s="7" t="n"/>
-      <c r="Z111" s="7" t="n"/>
+      <c r="U111" s="6" t="n"/>
+      <c r="V111" s="6" t="n"/>
+      <c r="W111" s="6" t="n"/>
+      <c r="X111" s="6" t="n"/>
+      <c r="Y111" s="6" t="n"/>
+      <c r="Z111" s="6" t="n"/>
     </row>
     <row r="112" ht="75" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -16329,12 +16378,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U112" s="7" t="n"/>
-      <c r="V112" s="7" t="n"/>
-      <c r="W112" s="7" t="n"/>
-      <c r="X112" s="7" t="n"/>
-      <c r="Y112" s="7" t="n"/>
-      <c r="Z112" s="7" t="n"/>
+      <c r="U112" s="6" t="n"/>
+      <c r="V112" s="6" t="n"/>
+      <c r="W112" s="6" t="n"/>
+      <c r="X112" s="6" t="n"/>
+      <c r="Y112" s="6" t="n"/>
+      <c r="Z112" s="6" t="n"/>
     </row>
     <row r="113" ht="75" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -16436,12 +16485,12 @@
           <t>с комплектом ответных фланцев</t>
         </is>
       </c>
-      <c r="U113" s="7" t="n"/>
-      <c r="V113" s="7" t="n"/>
-      <c r="W113" s="7" t="n"/>
-      <c r="X113" s="7" t="n"/>
-      <c r="Y113" s="7" t="n"/>
-      <c r="Z113" s="7" t="n"/>
+      <c r="U113" s="6" t="n"/>
+      <c r="V113" s="6" t="n"/>
+      <c r="W113" s="6" t="n"/>
+      <c r="X113" s="6" t="n"/>
+      <c r="Y113" s="6" t="n"/>
+      <c r="Z113" s="6" t="n"/>
     </row>
     <row r="114" ht="75" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -16547,12 +16596,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U114" s="7" t="n"/>
-      <c r="V114" s="7" t="n"/>
-      <c r="W114" s="7" t="n"/>
-      <c r="X114" s="7" t="n"/>
-      <c r="Y114" s="7" t="n"/>
-      <c r="Z114" s="7" t="n"/>
+      <c r="U114" s="6" t="n"/>
+      <c r="V114" s="6" t="n"/>
+      <c r="W114" s="6" t="n"/>
+      <c r="X114" s="6" t="n"/>
+      <c r="Y114" s="6" t="n"/>
+      <c r="Z114" s="6" t="n"/>
     </row>
     <row r="115" ht="75" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -16658,12 +16707,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U115" s="7" t="n"/>
-      <c r="V115" s="7" t="n"/>
-      <c r="W115" s="7" t="n"/>
-      <c r="X115" s="7" t="n"/>
-      <c r="Y115" s="7" t="n"/>
-      <c r="Z115" s="7" t="n"/>
+      <c r="U115" s="6" t="n"/>
+      <c r="V115" s="6" t="n"/>
+      <c r="W115" s="6" t="n"/>
+      <c r="X115" s="6" t="n"/>
+      <c r="Y115" s="6" t="n"/>
+      <c r="Z115" s="6" t="n"/>
     </row>
     <row r="116" ht="75" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -16769,12 +16818,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U116" s="7" t="n"/>
-      <c r="V116" s="7" t="n"/>
-      <c r="W116" s="7" t="n"/>
-      <c r="X116" s="7" t="n"/>
-      <c r="Y116" s="7" t="n"/>
-      <c r="Z116" s="7" t="n"/>
+      <c r="U116" s="6" t="n"/>
+      <c r="V116" s="6" t="n"/>
+      <c r="W116" s="6" t="n"/>
+      <c r="X116" s="6" t="n"/>
+      <c r="Y116" s="6" t="n"/>
+      <c r="Z116" s="6" t="n"/>
     </row>
     <row r="117" ht="75" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -16880,12 +16929,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U117" s="7" t="n"/>
-      <c r="V117" s="7" t="n"/>
-      <c r="W117" s="7" t="n"/>
-      <c r="X117" s="7" t="n"/>
-      <c r="Y117" s="7" t="n"/>
-      <c r="Z117" s="7" t="n"/>
+      <c r="U117" s="6" t="n"/>
+      <c r="V117" s="6" t="n"/>
+      <c r="W117" s="6" t="n"/>
+      <c r="X117" s="6" t="n"/>
+      <c r="Y117" s="6" t="n"/>
+      <c r="Z117" s="6" t="n"/>
     </row>
     <row r="118" ht="75" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -16983,12 +17032,12 @@
       </c>
       <c r="S118" s="3" t="inlineStr"/>
       <c r="T118" s="3" t="inlineStr"/>
-      <c r="U118" s="7" t="n"/>
-      <c r="V118" s="7" t="n"/>
-      <c r="W118" s="7" t="n"/>
-      <c r="X118" s="7" t="n"/>
-      <c r="Y118" s="7" t="n"/>
-      <c r="Z118" s="7" t="n"/>
+      <c r="U118" s="6" t="n"/>
+      <c r="V118" s="6" t="n"/>
+      <c r="W118" s="6" t="n"/>
+      <c r="X118" s="6" t="n"/>
+      <c r="Y118" s="6" t="n"/>
+      <c r="Z118" s="6" t="n"/>
     </row>
     <row r="119" ht="75" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -17079,12 +17128,12 @@
       </c>
       <c r="S119" s="3" t="inlineStr"/>
       <c r="T119" s="3" t="inlineStr"/>
-      <c r="U119" s="7" t="n"/>
-      <c r="V119" s="7" t="n"/>
-      <c r="W119" s="7" t="n"/>
-      <c r="X119" s="7" t="n"/>
-      <c r="Y119" s="7" t="n"/>
-      <c r="Z119" s="7" t="n"/>
+      <c r="U119" s="6" t="n"/>
+      <c r="V119" s="6" t="n"/>
+      <c r="W119" s="6" t="n"/>
+      <c r="X119" s="6" t="n"/>
+      <c r="Y119" s="6" t="n"/>
+      <c r="Z119" s="6" t="n"/>
     </row>
     <row r="120" ht="75" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -17178,12 +17227,12 @@
       </c>
       <c r="S120" s="3" t="inlineStr"/>
       <c r="T120" s="3" t="inlineStr"/>
-      <c r="U120" s="7" t="n"/>
-      <c r="V120" s="7" t="n"/>
-      <c r="W120" s="7" t="n"/>
-      <c r="X120" s="7" t="n"/>
-      <c r="Y120" s="7" t="n"/>
-      <c r="Z120" s="7" t="n"/>
+      <c r="U120" s="6" t="n"/>
+      <c r="V120" s="6" t="n"/>
+      <c r="W120" s="6" t="n"/>
+      <c r="X120" s="6" t="n"/>
+      <c r="Y120" s="6" t="n"/>
+      <c r="Z120" s="6" t="n"/>
     </row>
     <row r="121" ht="75" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -17277,12 +17326,12 @@
       </c>
       <c r="S121" s="3" t="inlineStr"/>
       <c r="T121" s="3" t="inlineStr"/>
-      <c r="U121" s="7" t="n"/>
-      <c r="V121" s="7" t="n"/>
-      <c r="W121" s="7" t="n"/>
-      <c r="X121" s="7" t="n"/>
-      <c r="Y121" s="7" t="n"/>
-      <c r="Z121" s="7" t="n"/>
+      <c r="U121" s="6" t="n"/>
+      <c r="V121" s="6" t="n"/>
+      <c r="W121" s="6" t="n"/>
+      <c r="X121" s="6" t="n"/>
+      <c r="Y121" s="6" t="n"/>
+      <c r="Z121" s="6" t="n"/>
     </row>
     <row r="122" ht="75" customHeight="1">
       <c r="A122" s="3" t="n">
@@ -17376,12 +17425,12 @@
       </c>
       <c r="S122" s="3" t="inlineStr"/>
       <c r="T122" s="3" t="inlineStr"/>
-      <c r="U122" s="7" t="n"/>
-      <c r="V122" s="7" t="n"/>
-      <c r="W122" s="7" t="n"/>
-      <c r="X122" s="7" t="n"/>
-      <c r="Y122" s="7" t="n"/>
-      <c r="Z122" s="7" t="n"/>
+      <c r="U122" s="6" t="n"/>
+      <c r="V122" s="6" t="n"/>
+      <c r="W122" s="6" t="n"/>
+      <c r="X122" s="6" t="n"/>
+      <c r="Y122" s="6" t="n"/>
+      <c r="Z122" s="6" t="n"/>
     </row>
     <row r="123" ht="75" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -17475,12 +17524,12 @@
       </c>
       <c r="S123" s="3" t="inlineStr"/>
       <c r="T123" s="3" t="inlineStr"/>
-      <c r="U123" s="7" t="n"/>
-      <c r="V123" s="7" t="n"/>
-      <c r="W123" s="7" t="n"/>
-      <c r="X123" s="7" t="n"/>
-      <c r="Y123" s="7" t="n"/>
-      <c r="Z123" s="7" t="n"/>
+      <c r="U123" s="6" t="n"/>
+      <c r="V123" s="6" t="n"/>
+      <c r="W123" s="6" t="n"/>
+      <c r="X123" s="6" t="n"/>
+      <c r="Y123" s="6" t="n"/>
+      <c r="Z123" s="6" t="n"/>
     </row>
     <row r="124" ht="75" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -17574,12 +17623,12 @@
       </c>
       <c r="S124" s="3" t="inlineStr"/>
       <c r="T124" s="3" t="inlineStr"/>
-      <c r="U124" s="7" t="n"/>
-      <c r="V124" s="7" t="n"/>
-      <c r="W124" s="7" t="n"/>
-      <c r="X124" s="7" t="n"/>
-      <c r="Y124" s="7" t="n"/>
-      <c r="Z124" s="7" t="n"/>
+      <c r="U124" s="6" t="n"/>
+      <c r="V124" s="6" t="n"/>
+      <c r="W124" s="6" t="n"/>
+      <c r="X124" s="6" t="n"/>
+      <c r="Y124" s="6" t="n"/>
+      <c r="Z124" s="6" t="n"/>
     </row>
     <row r="125" ht="75" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -17673,12 +17722,12 @@
       </c>
       <c r="S125" s="3" t="inlineStr"/>
       <c r="T125" s="3" t="inlineStr"/>
-      <c r="U125" s="7" t="n"/>
-      <c r="V125" s="7" t="n"/>
-      <c r="W125" s="7" t="n"/>
-      <c r="X125" s="7" t="n"/>
-      <c r="Y125" s="7" t="n"/>
-      <c r="Z125" s="7" t="n"/>
+      <c r="U125" s="6" t="n"/>
+      <c r="V125" s="6" t="n"/>
+      <c r="W125" s="6" t="n"/>
+      <c r="X125" s="6" t="n"/>
+      <c r="Y125" s="6" t="n"/>
+      <c r="Z125" s="6" t="n"/>
     </row>
     <row r="126" ht="75" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -17777,12 +17826,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U126" s="7" t="n"/>
-      <c r="V126" s="7" t="n"/>
-      <c r="W126" s="7" t="n"/>
-      <c r="X126" s="7" t="n"/>
-      <c r="Y126" s="7" t="n"/>
-      <c r="Z126" s="7" t="n"/>
+      <c r="U126" s="6" t="n"/>
+      <c r="V126" s="6" t="n"/>
+      <c r="W126" s="6" t="n"/>
+      <c r="X126" s="6" t="n"/>
+      <c r="Y126" s="6" t="n"/>
+      <c r="Z126" s="6" t="n"/>
     </row>
     <row r="127" ht="75" customHeight="1">
       <c r="A127" s="3" t="n">
@@ -17881,12 +17930,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U127" s="7" t="n"/>
-      <c r="V127" s="7" t="n"/>
-      <c r="W127" s="7" t="n"/>
-      <c r="X127" s="7" t="n"/>
-      <c r="Y127" s="7" t="n"/>
-      <c r="Z127" s="7" t="n"/>
+      <c r="U127" s="6" t="n"/>
+      <c r="V127" s="6" t="n"/>
+      <c r="W127" s="6" t="n"/>
+      <c r="X127" s="6" t="n"/>
+      <c r="Y127" s="6" t="n"/>
+      <c r="Z127" s="6" t="n"/>
     </row>
     <row r="128" ht="75" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -17985,12 +18034,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U128" s="7" t="n"/>
-      <c r="V128" s="7" t="n"/>
-      <c r="W128" s="7" t="n"/>
-      <c r="X128" s="7" t="n"/>
-      <c r="Y128" s="7" t="n"/>
-      <c r="Z128" s="7" t="n"/>
+      <c r="U128" s="6" t="n"/>
+      <c r="V128" s="6" t="n"/>
+      <c r="W128" s="6" t="n"/>
+      <c r="X128" s="6" t="n"/>
+      <c r="Y128" s="6" t="n"/>
+      <c r="Z128" s="6" t="n"/>
     </row>
     <row r="129" ht="75" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -18081,12 +18130,12 @@
       </c>
       <c r="S129" s="3" t="inlineStr"/>
       <c r="T129" s="3" t="inlineStr"/>
-      <c r="U129" s="7" t="n"/>
-      <c r="V129" s="7" t="n"/>
-      <c r="W129" s="7" t="n"/>
-      <c r="X129" s="7" t="n"/>
-      <c r="Y129" s="7" t="n"/>
-      <c r="Z129" s="7" t="n"/>
+      <c r="U129" s="6" t="n"/>
+      <c r="V129" s="6" t="n"/>
+      <c r="W129" s="6" t="n"/>
+      <c r="X129" s="6" t="n"/>
+      <c r="Y129" s="6" t="n"/>
+      <c r="Z129" s="6" t="n"/>
     </row>
     <row r="130" ht="75" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -18177,12 +18226,12 @@
       </c>
       <c r="S130" s="3" t="inlineStr"/>
       <c r="T130" s="3" t="inlineStr"/>
-      <c r="U130" s="7" t="n"/>
-      <c r="V130" s="7" t="n"/>
-      <c r="W130" s="7" t="n"/>
-      <c r="X130" s="7" t="n"/>
-      <c r="Y130" s="7" t="n"/>
-      <c r="Z130" s="7" t="n"/>
+      <c r="U130" s="6" t="n"/>
+      <c r="V130" s="6" t="n"/>
+      <c r="W130" s="6" t="n"/>
+      <c r="X130" s="6" t="n"/>
+      <c r="Y130" s="6" t="n"/>
+      <c r="Z130" s="6" t="n"/>
     </row>
     <row r="131" ht="75" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -18273,12 +18322,12 @@
       </c>
       <c r="S131" s="3" t="inlineStr"/>
       <c r="T131" s="3" t="inlineStr"/>
-      <c r="U131" s="7" t="n"/>
-      <c r="V131" s="7" t="n"/>
-      <c r="W131" s="7" t="n"/>
-      <c r="X131" s="7" t="n"/>
-      <c r="Y131" s="7" t="n"/>
-      <c r="Z131" s="7" t="n"/>
+      <c r="U131" s="6" t="n"/>
+      <c r="V131" s="6" t="n"/>
+      <c r="W131" s="6" t="n"/>
+      <c r="X131" s="6" t="n"/>
+      <c r="Y131" s="6" t="n"/>
+      <c r="Z131" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18562,12 +18611,12 @@
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="n"/>
-      <c r="Y4" s="7" t="n"/>
-      <c r="Z4" s="7" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -18668,12 +18717,12 @@
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -18764,12 +18813,12 @@
           <t>каталожный номер 065B7474</t>
         </is>
       </c>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
+      <c r="Z6" s="6" t="n"/>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -18860,12 +18909,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
-      <c r="Z7" s="7" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -18952,12 +19001,12 @@
           <t>Каталожный № 082X8477R</t>
         </is>
       </c>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -19049,12 +19098,12 @@
           <t>Затвор фланцевый 32нж910р Ду1000 Ру10 с эл.приводом с комплектом ответных фланцев (90 гр. указатель поворота- визуальны и встроенный дистанционный блок (токовый выход) указателя положения (открыто, закрыто)</t>
         </is>
       </c>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
+      <c r="Z9" s="6" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -19133,12 +19182,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
+      <c r="Z10" s="6" t="n"/>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -19217,12 +19266,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -19301,12 +19350,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
-      <c r="Z12" s="7" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -19405,12 +19454,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
+      <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -19493,12 +19542,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
     </row>
     <row r="15" ht="75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -19581,12 +19630,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
     </row>
     <row r="16" ht="75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -19669,12 +19718,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M40469</t>
         </is>
       </c>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
     </row>
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -19757,12 +19806,12 @@
           <t>Номинальное давление: 16 кгс/см2.Корпус: - Серый чугун GG25 • Высокопрочный чугун GGG40, Седло- EPDM HT; Диск - Нержавеющая сталь CF8M; PN 1,6; DN25–300; tраб. перекач. ср.: +60…+115°С; tмакс.: +130°С в кратковр. режиме tмин.: +40°С в кратковр. Режиме; каталожный номер BD01M38936</t>
         </is>
       </c>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="7" t="n"/>
-      <c r="Z17" s="7" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
     </row>
     <row r="18" ht="75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -19861,12 +19910,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="n"/>
-      <c r="X18" s="7" t="n"/>
-      <c r="Y18" s="7" t="n"/>
-      <c r="Z18" s="7" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -19965,12 +20014,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U19" s="7" t="n"/>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="n"/>
-      <c r="X19" s="7" t="n"/>
-      <c r="Y19" s="7" t="n"/>
-      <c r="Z19" s="7" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
     </row>
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -20069,12 +20118,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U20" s="7" t="n"/>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="n"/>
-      <c r="X20" s="7" t="n"/>
-      <c r="Y20" s="7" t="n"/>
-      <c r="Z20" s="7" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -20169,12 +20218,12 @@
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="7" t="n"/>
-      <c r="V21" s="7" t="n"/>
-      <c r="W21" s="7" t="n"/>
-      <c r="X21" s="7" t="n"/>
-      <c r="Y21" s="7" t="n"/>
-      <c r="Z21" s="7" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
     </row>
     <row r="22" ht="75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -20265,12 +20314,12 @@
       </c>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="7" t="n"/>
-      <c r="V22" s="7" t="n"/>
-      <c r="W22" s="7" t="n"/>
-      <c r="X22" s="7" t="n"/>
-      <c r="Y22" s="7" t="n"/>
-      <c r="Z22" s="7" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
     </row>
     <row r="23" ht="75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -20361,12 +20410,12 @@
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="7" t="n"/>
-      <c r="V23" s="7" t="n"/>
-      <c r="W23" s="7" t="n"/>
-      <c r="X23" s="7" t="n"/>
-      <c r="Y23" s="7" t="n"/>
-      <c r="Z23" s="7" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
     </row>
     <row r="24" ht="75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -20465,12 +20514,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
-      <c r="Z24" s="7" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
+      <c r="Z24" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20710,12 +20759,12 @@
           <t>Рыбозащитное устройство с потокообразователем РОП-200, под производительность насоса от 250 куб м/час. В комплекте переход на трубу ДУ 200 Материал изготовления ст.20. Покраска РОП — серебрянка. Диаметр заградительной ячейки — 4мм (длина защищаемой молоди рыбы длиной от 30мм)</t>
         </is>
       </c>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="n"/>
-      <c r="Y4" s="7" t="n"/>
-      <c r="Z4" s="7" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -20766,12 +20815,12 @@
           <t>Степень защиты IP 54, Питающее напряжение 230 V AC, Схема включения Z20, Выключающая сила 2 900 N, Макс. нагрузочная сила 2 500 N, Скорость управления 4 mm/min,  Электродвигатель 1 W, Выключение злектропривода от нагрузки Двухсиловое (Схема включения Z20 выключатели S1, S2), Рабочий ход с датчиком 25 mm, Датчик положения Электронный с R/I преобразователем с токовым сигналом С источником, Включение 2-проводник, Выход 4 - 20 mA, Схема включения Z269, Механическое присоединение Столбикы, Присоединительная высота 110мм, Прицоедин. резьба тяги M8x1-22, Эскиз P-1185/B, 2 добавочные выключатели положения, Схема включения Z21.</t>
         </is>
       </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -20866,12 +20915,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
+      <c r="Z6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
